--- a/league.xlsx
+++ b/league.xlsx
@@ -10,12 +10,14 @@
     <sheet name="青大会_blue1" r:id="rId5" sheetId="21"/>
     <sheet name="ダブルス大会_d1" r:id="rId6" sheetId="22"/>
     <sheet name="テスト大会_ratetest" r:id="rId7" sheetId="23"/>
+    <sheet name="ダブルス大会_2026092101" r:id="rId8" sheetId="24"/>
+    <sheet name="シングルス大会_20260921" r:id="rId9" sheetId="25"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5877" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48867" uniqueCount="551">
   <si>
     <t>青大会 (blue1)</t>
   </si>
@@ -765,6 +767,909 @@
   </si>
   <si>
     <t>シングルス / 5点1セット制 / 全3フェーズ / 3フェーズ消化</t>
+  </si>
+  <si>
+    <t>ダブルス大会 (2026092101)</t>
+  </si>
+  <si>
+    <t>ダブルス / 5点2セット制 / 全5フェーズ / 0フェーズ消化</t>
+  </si>
+  <si>
+    <t>○=勝ち ×=負け / セル=自分のセット数-相手のセット数</t>
+  </si>
+  <si>
+    <t>rlaiy &amp; hachi_18</t>
+  </si>
+  <si>
+    <t>omarupin &amp; pipis_57</t>
+  </si>
+  <si>
+    <t>AndroidA &amp; AndroidB</t>
+  </si>
+  <si>
+    <t>Jtype916 &amp; Alpha6000</t>
+  </si>
+  <si>
+    <t>nextbardo &amp; TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>1. rlaiy &amp; hachi_18</t>
+  </si>
+  <si>
+    <t>2. omarupin &amp; pipis_57</t>
+  </si>
+  <si>
+    <t>3. AndroidA &amp; AndroidB</t>
+  </si>
+  <si>
+    <t>4. LagnaKt &amp; M0nJ</t>
+  </si>
+  <si>
+    <t>5. Jtype916 &amp; Alpha6000</t>
+  </si>
+  <si>
+    <t>6. nextbardo &amp; TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>1位  rlaiy &amp; hachi_18</t>
+  </si>
+  <si>
+    <t>1位  omarupin &amp; pipis_57</t>
+  </si>
+  <si>
+    <t>1位  AndroidA &amp; AndroidB</t>
+  </si>
+  <si>
+    <t>1位  Jtype916 &amp; Alpha6000</t>
+  </si>
+  <si>
+    <t>1位  nextbardo &amp; TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>× 0-2</t>
+  </si>
+  <si>
+    <t>2位  rlaiy &amp; hachi_18</t>
+  </si>
+  <si>
+    <t>2位  omarupin &amp; pipis_57</t>
+  </si>
+  <si>
+    <t>2位  Jtype916 &amp; Alpha6000</t>
+  </si>
+  <si>
+    <t>2位  nextbardo &amp; TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>6位  AndroidA &amp; AndroidB</t>
+  </si>
+  <si>
+    <t>5-4 5-0</t>
+  </si>
+  <si>
+    <t>3位  omarupin &amp; pipis_57</t>
+  </si>
+  <si>
+    <t>3位  Jtype916 &amp; Alpha6000</t>
+  </si>
+  <si>
+    <t>5位  AndroidA &amp; AndroidB</t>
+  </si>
+  <si>
+    <t>5位  nextbardo &amp; TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>4位  omarupin &amp; pipis_57</t>
+  </si>
+  <si>
+    <t>4位  AndroidA &amp; AndroidB</t>
+  </si>
+  <si>
+    <t>4位  nextbardo &amp; TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>ダブルス / 5点2セット制 / 全5フェーズ / 1フェーズ消化</t>
+  </si>
+  <si>
+    <t>5-4 5-2</t>
+  </si>
+  <si>
+    <t>6位  nextbardo &amp; TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>× 1-2</t>
+  </si>
+  <si>
+    <t>2-5 5-3 5-3</t>
+  </si>
+  <si>
+    <t>3位  rlaiy &amp; hachi_18</t>
+  </si>
+  <si>
+    <t>1-5 5-4 5-1</t>
+  </si>
+  <si>
+    <t>ダブルス / 5点2セット制 / 全5フェーズ / 2フェーズ消化</t>
+  </si>
+  <si>
+    <t>5-2 5-3</t>
+  </si>
+  <si>
+    <t>5-3 1-5 5-4</t>
+  </si>
+  <si>
+    <t>0勝3敗  得失セット-4</t>
+  </si>
+  <si>
+    <t>ダブルス / 5点2セット制 / 全5フェーズ / 3フェーズ消化</t>
+  </si>
+  <si>
+    <t>Opanku &amp; AndroidB</t>
+  </si>
+  <si>
+    <t>3. Opanku &amp; AndroidB</t>
+  </si>
+  <si>
+    <t>6位  Opanku &amp; AndroidB</t>
+  </si>
+  <si>
+    <t>Opanku &amp; Dra_goons</t>
+  </si>
+  <si>
+    <t>3. Opanku &amp; Dra_goons</t>
+  </si>
+  <si>
+    <t>6位  Opanku &amp; Dra_goons</t>
+  </si>
+  <si>
+    <t>5-2 5-0</t>
+  </si>
+  <si>
+    <t>4勝0敗  得失セット+6</t>
+  </si>
+  <si>
+    <t>2位  LagnaKt &amp; M0nJ</t>
+  </si>
+  <si>
+    <t>3位  Opanku &amp; Dra_goons</t>
+  </si>
+  <si>
+    <t>5位  rlaiy &amp; hachi_18</t>
+  </si>
+  <si>
+    <t>1勝3敗  得失セット-3</t>
+  </si>
+  <si>
+    <t>1-5 5-3 5-2</t>
+  </si>
+  <si>
+    <t>2勝2敗  得失セット-1</t>
+  </si>
+  <si>
+    <t>4位  Opanku &amp; Dra_goons</t>
+  </si>
+  <si>
+    <t>ダブルス / 5点2セット制 / 全5フェーズ / 4フェーズ消化</t>
+  </si>
+  <si>
+    <t>5-3 5-2</t>
+  </si>
+  <si>
+    <t>1勝4敗  得失セット-5</t>
+  </si>
+  <si>
+    <t>1勝4敗  得失セット-7</t>
+  </si>
+  <si>
+    <t>5-3 3-5 5-3</t>
+  </si>
+  <si>
+    <t>5勝0敗  得失セット+7</t>
+  </si>
+  <si>
+    <t>ダブルス / 5点2セット制 / 全5フェーズ / 5フェーズ消化</t>
+  </si>
+  <si>
+    <t>シングルス大会 (20260921)</t>
+  </si>
+  <si>
+    <t>シングルス / 5点1セット制(デュース) / 全13フェーズ / 0フェーズ消化</t>
+  </si>
+  <si>
+    <t>hachi_18</t>
+  </si>
+  <si>
+    <t>TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>Opanku</t>
+  </si>
+  <si>
+    <t>azisaba3</t>
+  </si>
+  <si>
+    <t>Dra_goons</t>
+  </si>
+  <si>
+    <t>2. hachi_18</t>
+  </si>
+  <si>
+    <t>3. TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>4. pipis_57</t>
+  </si>
+  <si>
+    <t>5. omarupin</t>
+  </si>
+  <si>
+    <t>6. Jtype916</t>
+  </si>
+  <si>
+    <t>7. M0nJ</t>
+  </si>
+  <si>
+    <t>8. sota2486</t>
+  </si>
+  <si>
+    <t>9. Alpha6000</t>
+  </si>
+  <si>
+    <t>10. Opanku</t>
+  </si>
+  <si>
+    <t>11. azisaba3</t>
+  </si>
+  <si>
+    <t>12. Dra_goons</t>
+  </si>
+  <si>
+    <t>13. AndroidA</t>
+  </si>
+  <si>
+    <t>14. AndroidB</t>
+  </si>
+  <si>
+    <t>1位  hachi_18</t>
+  </si>
+  <si>
+    <t>1位  TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>1位  Opanku</t>
+  </si>
+  <si>
+    <t>1位  azisaba3</t>
+  </si>
+  <si>
+    <t>1位  Dra_goons</t>
+  </si>
+  <si>
+    <t>1位  AndroidB</t>
+  </si>
+  <si>
+    <t>14位</t>
+  </si>
+  <si>
+    <t>5-0</t>
+  </si>
+  <si>
+    <t>2位  hachi_18</t>
+  </si>
+  <si>
+    <t>2位  TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>2位  Opanku</t>
+  </si>
+  <si>
+    <t>2位  azisaba3</t>
+  </si>
+  <si>
+    <t>2位  Dra_goons</t>
+  </si>
+  <si>
+    <t>14位  AndroidB</t>
+  </si>
+  <si>
+    <t>13位</t>
+  </si>
+  <si>
+    <t>3位  TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>3位  pipis_57</t>
+  </si>
+  <si>
+    <t>3位  Opanku</t>
+  </si>
+  <si>
+    <t>3位  azisaba3</t>
+  </si>
+  <si>
+    <t>3位  Dra_goons</t>
+  </si>
+  <si>
+    <t>13位  hachi_18</t>
+  </si>
+  <si>
+    <t>13位  AndroidB</t>
+  </si>
+  <si>
+    <t>12位</t>
+  </si>
+  <si>
+    <t>4位  omarupin</t>
+  </si>
+  <si>
+    <t>4位  sota2486</t>
+  </si>
+  <si>
+    <t>4位  Opanku</t>
+  </si>
+  <si>
+    <t>4位  azisaba3</t>
+  </si>
+  <si>
+    <t>12位  hachi_18</t>
+  </si>
+  <si>
+    <t>12位  Dra_goons</t>
+  </si>
+  <si>
+    <t>12位  AndroidB</t>
+  </si>
+  <si>
+    <t>11位</t>
+  </si>
+  <si>
+    <t>5位  Jtype916</t>
+  </si>
+  <si>
+    <t>5位  sota2486</t>
+  </si>
+  <si>
+    <t>5位  Alpha6000</t>
+  </si>
+  <si>
+    <t>5位  azisaba3</t>
+  </si>
+  <si>
+    <t>11位  hachi_18</t>
+  </si>
+  <si>
+    <t>11位  omarupin</t>
+  </si>
+  <si>
+    <t>11位  Dra_goons</t>
+  </si>
+  <si>
+    <t>11位  AndroidB</t>
+  </si>
+  <si>
+    <t>10位</t>
+  </si>
+  <si>
+    <t>6位  Jtype916</t>
+  </si>
+  <si>
+    <t>6位  M0nJ</t>
+  </si>
+  <si>
+    <t>6位  sota2486</t>
+  </si>
+  <si>
+    <t>6位  Alpha6000</t>
+  </si>
+  <si>
+    <t>10位  hachi_18</t>
+  </si>
+  <si>
+    <t>10位  omarupin</t>
+  </si>
+  <si>
+    <t>10位  azisaba3</t>
+  </si>
+  <si>
+    <t>10位  Dra_goons</t>
+  </si>
+  <si>
+    <t>10位  AndroidB</t>
+  </si>
+  <si>
+    <t>9位</t>
+  </si>
+  <si>
+    <t>6-4</t>
+  </si>
+  <si>
+    <t>7位  M0nJ</t>
+  </si>
+  <si>
+    <t>7位  sota2486</t>
+  </si>
+  <si>
+    <t>9位  hachi_18</t>
+  </si>
+  <si>
+    <t>9位  omarupin</t>
+  </si>
+  <si>
+    <t>9位  Jtype916</t>
+  </si>
+  <si>
+    <t>9位  azisaba3</t>
+  </si>
+  <si>
+    <t>9位  Dra_goons</t>
+  </si>
+  <si>
+    <t>9位  AndroidB</t>
+  </si>
+  <si>
+    <t>8位</t>
+  </si>
+  <si>
+    <t>8位  hachi_18</t>
+  </si>
+  <si>
+    <t>8位  omarupin</t>
+  </si>
+  <si>
+    <t>8位  Jtype916</t>
+  </si>
+  <si>
+    <t>8位  M0nJ</t>
+  </si>
+  <si>
+    <t>8位  azisaba3</t>
+  </si>
+  <si>
+    <t>8位  Dra_goons</t>
+  </si>
+  <si>
+    <t>8位  AndroidB</t>
+  </si>
+  <si>
+    <t>シングルス / 5点1セット制(デュース) / 全13フェーズ / 1フェーズ消化</t>
+  </si>
+  <si>
+    <t>Pen4</t>
+  </si>
+  <si>
+    <t>13. AndroidA (交代前)</t>
+  </si>
+  <si>
+    <t>15. Pen4 (交代)</t>
+  </si>
+  <si>
+    <t>8位  Pen4</t>
+  </si>
+  <si>
+    <t>9位  M0nJ</t>
+  </si>
+  <si>
+    <t>15位</t>
+  </si>
+  <si>
+    <t>9位  Pen4</t>
+  </si>
+  <si>
+    <t>10位  Jtype916</t>
+  </si>
+  <si>
+    <t>10位  M0nJ</t>
+  </si>
+  <si>
+    <t>15位  azisaba3</t>
+  </si>
+  <si>
+    <t>10位  Pen4</t>
+  </si>
+  <si>
+    <t>11位  Jtype916</t>
+  </si>
+  <si>
+    <t>11位  M0nJ</t>
+  </si>
+  <si>
+    <t>14位  azisaba3</t>
+  </si>
+  <si>
+    <t>14位  Dra_goons</t>
+  </si>
+  <si>
+    <t>7位  hachi_18</t>
+  </si>
+  <si>
+    <t>7位  Alpha6000</t>
+  </si>
+  <si>
+    <t>7位  AndroidB</t>
+  </si>
+  <si>
+    <t>7位  Jtype916</t>
+  </si>
+  <si>
+    <t>11位  Pen4</t>
+  </si>
+  <si>
+    <t>13位  M0nJ</t>
+  </si>
+  <si>
+    <t>13位  azisaba3</t>
+  </si>
+  <si>
+    <t>13位  Dra_goons</t>
+  </si>
+  <si>
+    <t>4位  TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>4位  AndroidA</t>
+  </si>
+  <si>
+    <t>12位  omarupin</t>
+  </si>
+  <si>
+    <t>12位  M0nJ</t>
+  </si>
+  <si>
+    <t>12位  azisaba3</t>
+  </si>
+  <si>
+    <t>8-6</t>
+  </si>
+  <si>
+    <t>5位  AndroidA</t>
+  </si>
+  <si>
+    <t>6位  hachi_18</t>
+  </si>
+  <si>
+    <t>6位  Opanku</t>
+  </si>
+  <si>
+    <t>シングルス / 5点1セット制(デュース) / 全13フェーズ / 2フェーズ消化</t>
+  </si>
+  <si>
+    <t>6位  AndroidA</t>
+  </si>
+  <si>
+    <t>7位  Opanku</t>
+  </si>
+  <si>
+    <t>7位  AndroidA</t>
+  </si>
+  <si>
+    <t>8位  Opanku</t>
+  </si>
+  <si>
+    <t>15位  omarupin</t>
+  </si>
+  <si>
+    <t>14位  omarupin</t>
+  </si>
+  <si>
+    <t>13位  omarupin</t>
+  </si>
+  <si>
+    <t>8位  AndroidA</t>
+  </si>
+  <si>
+    <t>10位  Opanku</t>
+  </si>
+  <si>
+    <t>シングルス / 5点1セット制(デュース) / 全13フェーズ / 3フェーズ消化</t>
+  </si>
+  <si>
+    <t>7位  TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>4勝0敗  得失セット+4</t>
+  </si>
+  <si>
+    <t>0勝4敗  得失セット-4</t>
+  </si>
+  <si>
+    <t>9位  AndroidA</t>
+  </si>
+  <si>
+    <t>6位  TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>シングルス / 5点1セット制(デュース) / 全13フェーズ / 4フェーズ消化</t>
+  </si>
+  <si>
+    <t>1勝4敗  得失セット-3</t>
+  </si>
+  <si>
+    <t>4勝1敗  得失セット+3</t>
+  </si>
+  <si>
+    <t>0勝5敗  得失セット-5</t>
+  </si>
+  <si>
+    <t>5位  TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>5勝0敗  得失セット+5</t>
+  </si>
+  <si>
+    <t>10位  AndroidA</t>
+  </si>
+  <si>
+    <t>2勝3敗  得失セット-1</t>
+  </si>
+  <si>
+    <t>シングルス / 5点1セット制(デュース) / 全13フェーズ / 5フェーズ消化</t>
+  </si>
+  <si>
+    <t>5位  Pen4</t>
+  </si>
+  <si>
+    <t>9位  Opanku</t>
+  </si>
+  <si>
+    <t>1勝5敗  得失セット-4</t>
+  </si>
+  <si>
+    <t>-6</t>
+  </si>
+  <si>
+    <t>4勝2敗  得失セット+2</t>
+  </si>
+  <si>
+    <t>6位  Pen4</t>
+  </si>
+  <si>
+    <t>0勝6敗  得失セット-6</t>
+  </si>
+  <si>
+    <t>8位  TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>3勝3敗  得失セット+0</t>
+  </si>
+  <si>
+    <t>2勝4敗  得失セット-2</t>
+  </si>
+  <si>
+    <t>11位  AndroidA</t>
+  </si>
+  <si>
+    <t>6勝0敗  得失セット+6</t>
+  </si>
+  <si>
+    <t>5勝1敗  得失セット+4</t>
+  </si>
+  <si>
+    <t>15位  Dra_goons</t>
+  </si>
+  <si>
+    <t>7-5</t>
+  </si>
+  <si>
+    <t>7位  Pen4</t>
+  </si>
+  <si>
+    <t>シングルス / 5点1セット制(デュース) / 全13フェーズ / 6フェーズ消化</t>
+  </si>
+  <si>
+    <t>11位  azisaba3</t>
+  </si>
+  <si>
+    <t>2勝5敗  得失セット-3</t>
+  </si>
+  <si>
+    <t>12位  AndroidA</t>
+  </si>
+  <si>
+    <t>1勝6敗  得失セット-5</t>
+  </si>
+  <si>
+    <t>6勝1敗  得失セット+5</t>
+  </si>
+  <si>
+    <t>4位  Pen4</t>
+  </si>
+  <si>
+    <t>3勝4敗  得失セット-1</t>
+  </si>
+  <si>
+    <t>5勝2敗  得失セット+3</t>
+  </si>
+  <si>
+    <t>0勝7敗  得失セット-7</t>
+  </si>
+  <si>
+    <t>4勝3敗  得失セット+1</t>
+  </si>
+  <si>
+    <t>シングルス / 5点1セット制(デュース) / 全13フェーズ / 7フェーズ消化</t>
+  </si>
+  <si>
+    <t>2勝6敗  得失セット-4</t>
+  </si>
+  <si>
+    <t>1勝7敗  得失セット-6</t>
+  </si>
+  <si>
+    <t>4勝4敗  得失セット+0</t>
+  </si>
+  <si>
+    <t>7勝1敗  得失セット+6</t>
+  </si>
+  <si>
+    <t>14位  M0nJ</t>
+  </si>
+  <si>
+    <t>5勝3敗  得失セット+2</t>
+  </si>
+  <si>
+    <t>シングルス / 5点1セット制(デュース) / 全13フェーズ / 8フェーズ消化</t>
+  </si>
+  <si>
+    <t>8勝1敗  得失セット+7</t>
+  </si>
+  <si>
+    <t>4勝5敗  得失セット-1</t>
+  </si>
+  <si>
+    <t>5勝4敗  得失セット+1</t>
+  </si>
+  <si>
+    <t>9位  TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>2勝7敗  得失セット-5</t>
+  </si>
+  <si>
+    <t>6勝2敗  得失セット+4</t>
+  </si>
+  <si>
+    <t>1勝8敗  得失セット-7</t>
+  </si>
+  <si>
+    <t>6勝3敗  得失セット+3</t>
+  </si>
+  <si>
+    <t>7位  pipis_57</t>
+  </si>
+  <si>
+    <t>13位  AndroidA</t>
+  </si>
+  <si>
+    <t>シングルス / 5点1セット制(デュース) / 全13フェーズ / 9フェーズ消化</t>
+  </si>
+  <si>
+    <t>-8</t>
+  </si>
+  <si>
+    <t>9勝1敗  得失セット+8</t>
+  </si>
+  <si>
+    <t>1勝9敗  得失セット-8</t>
+  </si>
+  <si>
+    <t>4勝6敗  得失セット-2</t>
+  </si>
+  <si>
+    <t>3勝7敗  得失セット-4</t>
+  </si>
+  <si>
+    <t>7勝2敗  得失セット+5</t>
+  </si>
+  <si>
+    <t>5勝5敗  得失セット+0</t>
+  </si>
+  <si>
+    <t>2勝8敗  得失セット-6</t>
+  </si>
+  <si>
+    <t>14位  AndroidA</t>
+  </si>
+  <si>
+    <t>6勝4敗  得失セット+2</t>
+  </si>
+  <si>
+    <t>シングルス / 5点1セット制(デュース) / 全13フェーズ / 10フェーズ消化</t>
+  </si>
+  <si>
+    <t>10勝1敗  得失セット+9</t>
+  </si>
+  <si>
+    <t>2勝9敗  得失セット-7</t>
+  </si>
+  <si>
+    <t>6勝5敗  得失セット+1</t>
+  </si>
+  <si>
+    <t>4勝7敗  得失セット-3</t>
+  </si>
+  <si>
+    <t>15位  AndroidA</t>
+  </si>
+  <si>
+    <t>5勝6敗  得失セット-1</t>
+  </si>
+  <si>
+    <t>7勝3敗  得失セット+4</t>
+  </si>
+  <si>
+    <t>5位  Opanku</t>
+  </si>
+  <si>
+    <t>10位  TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>シングルス / 5点1セット制(デュース) / 全13フェーズ / 11フェーズ消化</t>
+  </si>
+  <si>
+    <t>7勝5敗  得失セット+2</t>
+  </si>
+  <si>
+    <t>14位  hachi_18</t>
+  </si>
+  <si>
+    <t>2勝10敗  得失セット-8</t>
+  </si>
+  <si>
+    <t>+10</t>
+  </si>
+  <si>
+    <t>11勝1敗  得失セット+10</t>
+  </si>
+  <si>
+    <t>6勝6敗  得失セット+0</t>
+  </si>
+  <si>
+    <t>8勝3敗  得失セット+5</t>
+  </si>
+  <si>
+    <t>5勝7敗  得失セット-2</t>
+  </si>
+  <si>
+    <t>3勝9敗  得失セット-6</t>
+  </si>
+  <si>
+    <t>10勝2敗  得失セット+8</t>
+  </si>
+  <si>
+    <t>シングルス / 5点1セット制(デュース) / 全13フェーズ / 12フェーズ消化</t>
+  </si>
+  <si>
+    <t>6勝7敗  得失セット-1</t>
+  </si>
+  <si>
+    <t>2勝11敗  得失セット-9</t>
+  </si>
+  <si>
+    <t>11勝2敗  得失セット+9</t>
+  </si>
+  <si>
+    <t>8勝5敗  得失セット+3</t>
+  </si>
+  <si>
+    <t>8勝4敗  得失セット+4</t>
+  </si>
+  <si>
+    <t>3勝10敗  得失セット-7</t>
+  </si>
+  <si>
+    <t>7勝6敗  得失セット+1</t>
+  </si>
+  <si>
+    <t>5勝8敗  得失セット-3</t>
+  </si>
+  <si>
+    <t>+11</t>
+  </si>
+  <si>
+    <t>12勝1敗  得失セット+11</t>
+  </si>
+  <si>
+    <t>シングルス / 5点1セット制(デュース) / 全13フェーズ / 13フェーズ消化</t>
   </si>
 </sst>
 </file>
@@ -772,13 +1677,1978 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="205">
+  <fonts count="598">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -1856,7 +4726,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="613">
+  <cellXfs count="1792">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -3147,6 +6017,2495 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="203" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="205" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="205" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="205" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="207" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="206" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="208" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="208" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="208" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="210" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="209" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="211" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="211" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="211" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="213" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="212" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="214" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="214" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="214" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="216" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="215" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="217" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="217" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="217" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="219" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="218" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="220" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="220" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="220" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="222" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="221" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="223" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="223" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="223" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="225" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="224" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="226" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="226" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="226" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="228" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="227" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="229" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="229" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="229" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="231" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="230" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="232" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="232" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="232" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="234" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="233" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="235" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="235" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="235" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="237" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="236" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="238" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="238" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="238" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="240" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="239" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="241" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="241" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="241" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="243" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="242" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="244" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="244" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="244" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="246" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="245" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="247" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="247" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="247" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="249" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="248" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="250" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="250" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="250" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="252" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="251" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="253" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="253" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="253" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="255" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="254" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="256" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="256" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="256" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="258" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="257" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="259" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="259" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="259" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="261" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="260" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="262" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="262" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="262" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="264" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="263" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="265" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="265" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="265" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="267" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="266" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="268" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="268" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="268" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="270" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="269" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="271" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="271" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="271" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="273" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="272" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="274" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="274" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="274" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="276" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="275" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="277" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="277" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="277" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="279" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="278" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="280" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="280" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="280" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="282" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="281" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="283" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="283" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="283" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="285" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="284" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="286" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="286" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="286" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="288" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="287" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="289" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="289" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="289" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="291" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="290" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="292" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="292" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="292" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="294" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="293" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="295" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="295" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="295" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="297" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="296" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="298" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="298" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="298" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="300" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="299" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="301" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="301" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="301" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="303" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="302" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="304" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="304" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="304" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="306" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="305" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="307" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="307" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="307" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="309" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="308" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="310" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="310" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="310" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="312" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="311" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="313" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="313" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="313" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="315" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="314" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="316" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="316" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="316" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="318" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="317" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="319" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="319" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="319" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="321" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="320" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="322" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="322" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="322" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="324" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="323" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="325" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="325" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="325" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="327" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="326" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="328" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="328" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="328" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="330" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="329" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="331" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="331" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="331" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="333" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="332" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="334" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="334" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="334" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="336" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="335" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="337" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="337" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="337" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="339" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="338" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="340" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="340" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="340" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="342" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="341" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="343" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="343" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="343" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="345" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="344" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="346" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="346" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="346" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="348" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="347" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="349" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="349" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="349" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="351" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="350" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="352" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="352" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="352" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="354" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="353" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="355" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="355" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="355" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="357" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="356" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="358" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="358" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="358" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="360" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="359" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="361" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="361" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="361" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="363" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="362" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="364" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="364" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="364" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="366" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="365" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="367" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="367" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="367" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="369" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="368" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="370" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="370" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="370" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="372" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="371" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="373" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="373" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="373" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="375" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="374" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="376" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="376" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="376" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="378" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="377" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="379" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="379" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="379" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="381" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="380" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="382" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="382" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="382" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="384" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="383" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="385" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="385" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="385" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="387" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="386" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="388" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="388" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="388" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="390" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="389" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="391" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="391" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="391" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="393" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="392" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="394" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="394" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="394" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="396" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="395" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="397" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="397" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="397" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="399" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="398" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="400" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="400" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="400" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="402" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="401" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="403" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="403" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="403" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="405" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="404" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="406" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="406" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="406" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="408" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="407" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="409" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="409" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="409" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="411" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="410" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="412" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="412" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="412" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="414" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="413" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="415" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="415" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="415" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="417" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="416" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="418" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="418" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="418" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="420" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="419" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="421" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="421" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="421" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="423" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="422" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="424" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="424" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="424" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="426" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="425" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="427" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="427" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="427" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="429" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="428" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="430" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="430" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="430" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="432" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="431" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="433" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="433" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="433" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="435" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="434" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="436" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="436" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="436" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="438" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="437" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="439" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="439" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="439" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="441" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="440" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="442" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="442" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="442" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="444" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="443" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="445" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="445" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="445" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="447" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="446" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="448" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="448" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="448" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="450" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="449" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="451" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="451" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="451" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="453" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="452" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="454" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="454" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="454" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="456" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="455" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="457" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="457" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="457" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="459" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="458" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="460" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="460" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="460" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="462" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="461" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="463" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="463" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="463" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="465" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="464" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="466" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="466" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="466" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="468" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="467" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="469" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="469" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="469" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="471" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="470" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="472" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="472" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="472" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="474" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="473" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="475" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="475" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="475" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="477" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="476" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="478" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="478" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="478" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="480" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="479" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="481" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="481" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="481" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="483" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="482" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="484" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="484" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="484" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="486" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="485" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="487" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="487" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="487" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="489" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="488" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="490" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="490" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="490" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="492" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="491" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="493" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="493" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="493" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="495" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="494" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="496" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="496" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="496" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="498" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="497" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="499" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="499" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="499" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="501" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="500" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="502" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="502" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="502" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="504" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="503" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="505" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="505" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="505" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="507" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="506" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="508" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="508" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="508" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="510" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="509" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="511" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="511" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="511" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="513" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="512" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="514" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="514" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="514" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="516" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="515" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="517" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="517" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="517" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="519" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="518" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="520" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="520" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="520" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="522" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="521" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="523" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="523" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="523" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="525" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="524" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="526" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="526" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="526" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="528" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="527" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="529" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="529" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="529" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="531" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="530" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="532" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="532" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="532" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="534" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="533" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="535" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="535" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="535" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="537" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="536" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="538" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="540" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="539" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="541" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="543" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="542" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="544" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="546" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="545" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="547" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="549" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="548" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="550" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="552" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="551" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="553" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="555" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="554" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="556" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="558" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="557" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="559" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="561" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="560" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="562" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="562" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="562" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="564" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="563" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="565" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="565" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="565" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="567" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="566" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="568" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="568" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="568" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="570" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="569" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="571" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="571" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="571" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="573" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="572" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="574" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="574" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="574" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="576" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="575" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="577" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="577" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="577" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="579" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="578" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="580" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="580" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="580" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="582" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="581" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="583" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="583" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="583" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="585" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="584" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="586" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="586" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="586" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="588" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="587" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="589" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="589" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="589" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="591" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="590" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="592" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="592" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="592" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="594" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="593" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="595" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="595" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="595" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="597" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="596" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
@@ -4620,307 +9979,3231 @@
   <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
+    <col min="1" max="1" customWidth="true" width="23.4375"/>
+    <col min="2" max="2" customWidth="true" width="16.40625"/>
+    <col min="3" max="3" customWidth="true" width="16.40625"/>
+    <col min="4" max="4" customWidth="true" width="16.40625"/>
+    <col min="5" max="5" customWidth="true" width="16.40625"/>
+    <col min="6" max="6" customWidth="true" width="6.25"/>
+    <col min="7" max="7" customWidth="true" width="6.25"/>
+    <col min="8" max="8" customWidth="true" width="6.25"/>
+    <col min="9" max="9" customWidth="true" width="6.25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="604">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="605">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="605">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="607">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s" s="607">
+        <v>225</v>
+      </c>
+      <c r="C5" t="s" s="607">
+        <v>226</v>
+      </c>
+      <c r="D5" t="s" s="607">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s" s="607">
+        <v>38</v>
+      </c>
+      <c r="F5" t="s" s="607">
+        <v>10</v>
+      </c>
+      <c r="G5" t="s" s="607">
+        <v>11</v>
+      </c>
+      <c r="H5" t="s" s="607">
+        <v>12</v>
+      </c>
+      <c r="I5" t="s" s="607">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="608">
+        <v>227</v>
+      </c>
+      <c r="B6" s="612"/>
+      <c r="C6" t="s" s="611">
+        <v>233</v>
+      </c>
+      <c r="D6" t="s" s="610">
+        <v>234</v>
+      </c>
+      <c r="E6" t="s" s="611">
+        <v>233</v>
+      </c>
+      <c r="F6" t="n" s="609">
+        <v>1.0</v>
+      </c>
+      <c r="G6" t="n" s="609">
+        <v>2.0</v>
+      </c>
+      <c r="H6" t="s" s="609">
+        <v>89</v>
+      </c>
+      <c r="I6" t="s" s="609">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="608">
+        <v>228</v>
+      </c>
+      <c r="B7" t="s" s="610">
+        <v>234</v>
+      </c>
+      <c r="C7" s="612"/>
+      <c r="D7" t="s" s="610">
+        <v>234</v>
+      </c>
+      <c r="E7" t="s" s="611">
+        <v>233</v>
+      </c>
+      <c r="F7" t="n" s="609">
+        <v>2.0</v>
+      </c>
+      <c r="G7" t="n" s="609">
+        <v>1.0</v>
+      </c>
+      <c r="H7" t="s" s="609">
+        <v>91</v>
+      </c>
+      <c r="I7" t="s" s="609">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="608">
+        <v>229</v>
+      </c>
+      <c r="B8" t="s" s="611">
+        <v>233</v>
+      </c>
+      <c r="C8" t="s" s="611">
+        <v>233</v>
+      </c>
+      <c r="D8" s="612"/>
+      <c r="E8" t="s" s="611">
+        <v>233</v>
+      </c>
+      <c r="F8" t="n" s="609">
+        <v>0.0</v>
+      </c>
+      <c r="G8" t="n" s="609">
+        <v>3.0</v>
+      </c>
+      <c r="H8" t="s" s="609">
+        <v>139</v>
+      </c>
+      <c r="I8" t="s" s="609">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="608">
+        <v>230</v>
+      </c>
+      <c r="B9" t="s" s="610">
+        <v>234</v>
+      </c>
+      <c r="C9" t="s" s="610">
+        <v>234</v>
+      </c>
+      <c r="D9" t="s" s="610">
+        <v>234</v>
+      </c>
+      <c r="E9" s="612"/>
+      <c r="F9" t="n" s="609">
+        <v>3.0</v>
+      </c>
+      <c r="G9" t="n" s="609">
+        <v>0.0</v>
+      </c>
+      <c r="H9" t="s" s="609">
+        <v>127</v>
+      </c>
+      <c r="I9" t="s" s="609">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="606">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="607">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s" s="607">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s" s="607">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s" s="607">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="605">
+        <v>226</v>
+      </c>
+      <c r="B14" t="s" s="605">
+        <v>225</v>
+      </c>
+      <c r="C14" t="s" s="605">
+        <v>235</v>
+      </c>
+      <c r="D14" t="s" s="605">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="605">
+        <v>225</v>
+      </c>
+      <c r="B15" t="s" s="605">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s" s="605">
+        <v>235</v>
+      </c>
+      <c r="D15" t="s" s="605">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="605">
+        <v>38</v>
+      </c>
+      <c r="B16" t="s" s="605">
+        <v>225</v>
+      </c>
+      <c r="C16" t="s" s="605">
+        <v>235</v>
+      </c>
+      <c r="D16" t="s" s="605">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="605">
+        <v>226</v>
+      </c>
+      <c r="B17" t="s" s="605">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s" s="605">
+        <v>235</v>
+      </c>
+      <c r="D17" t="s" s="605">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="605">
+        <v>38</v>
+      </c>
+      <c r="B18" t="s" s="605">
+        <v>226</v>
+      </c>
+      <c r="C18" t="s" s="605">
+        <v>235</v>
+      </c>
+      <c r="D18" t="s" s="605">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="605">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s" s="605">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s" s="605">
+        <v>235</v>
+      </c>
+      <c r="D19" t="s" s="605">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="606">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="605">
+        <v>48</v>
+      </c>
+      <c r="B22" t="s" s="605">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="605">
+        <v>237</v>
+      </c>
+      <c r="B23" t="s" s="605">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="605">
+        <v>240</v>
+      </c>
+      <c r="B24" t="s" s="605">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="605">
+        <v>100</v>
+      </c>
+      <c r="B25" t="s" s="605">
+        <v>221</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:K38"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" width="23.4375"/>
+    <col min="2" max="2" customWidth="true" width="16.40625"/>
+    <col min="3" max="3" customWidth="true" width="16.40625"/>
+    <col min="4" max="4" customWidth="true" width="16.40625"/>
+    <col min="5" max="5" customWidth="true" width="16.40625"/>
+    <col min="6" max="6" customWidth="true" width="16.40625"/>
+    <col min="7" max="7" customWidth="true" width="16.40625"/>
+    <col min="8" max="8" customWidth="true" width="6.25"/>
+    <col min="9" max="9" customWidth="true" width="6.25"/>
+    <col min="10" max="10" customWidth="true" width="6.25"/>
+    <col min="11" max="11" customWidth="true" width="6.25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="820">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="821">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="821">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="823">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s" s="823">
+        <v>253</v>
+      </c>
+      <c r="C5" t="s" s="823">
+        <v>254</v>
+      </c>
+      <c r="D5" t="s" s="823">
+        <v>298</v>
+      </c>
+      <c r="E5" t="s" s="823">
+        <v>194</v>
+      </c>
+      <c r="F5" t="s" s="823">
+        <v>256</v>
+      </c>
+      <c r="G5" t="s" s="823">
+        <v>257</v>
+      </c>
+      <c r="H5" t="s" s="823">
+        <v>10</v>
+      </c>
+      <c r="I5" t="s" s="823">
+        <v>11</v>
+      </c>
+      <c r="J5" t="s" s="823">
+        <v>12</v>
+      </c>
+      <c r="K5" t="s" s="823">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="824">
+        <v>258</v>
+      </c>
+      <c r="B6" s="828"/>
+      <c r="C6" t="s" s="827">
+        <v>269</v>
+      </c>
+      <c r="D6" t="s" s="827">
+        <v>269</v>
+      </c>
+      <c r="E6" t="s" s="827">
+        <v>269</v>
+      </c>
+      <c r="F6" t="s" s="827">
+        <v>286</v>
+      </c>
+      <c r="G6" t="s" s="826">
+        <v>59</v>
+      </c>
+      <c r="H6" t="n" s="825">
+        <v>1.0</v>
+      </c>
+      <c r="I6" t="n" s="825">
+        <v>4.0</v>
+      </c>
+      <c r="J6" t="s" s="825">
+        <v>136</v>
+      </c>
+      <c r="K6" t="s" s="825">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="824">
+        <v>259</v>
+      </c>
+      <c r="B7" t="s" s="826">
+        <v>59</v>
+      </c>
+      <c r="C7" s="828"/>
+      <c r="D7" t="s" s="826">
+        <v>90</v>
+      </c>
+      <c r="E7" t="s" s="826">
+        <v>90</v>
+      </c>
+      <c r="F7" t="s" s="827">
+        <v>269</v>
+      </c>
+      <c r="G7" t="s" s="827">
+        <v>286</v>
+      </c>
+      <c r="H7" t="n" s="825">
+        <v>3.0</v>
+      </c>
+      <c r="I7" t="n" s="825">
+        <v>2.0</v>
+      </c>
+      <c r="J7" t="s" s="825">
+        <v>91</v>
+      </c>
+      <c r="K7" t="s" s="825">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="824">
+        <v>299</v>
+      </c>
+      <c r="B8" t="s" s="826">
+        <v>59</v>
+      </c>
+      <c r="C8" t="s" s="827">
+        <v>286</v>
+      </c>
+      <c r="D8" s="828"/>
+      <c r="E8" t="s" s="827">
+        <v>269</v>
+      </c>
+      <c r="F8" t="s" s="827">
+        <v>286</v>
+      </c>
+      <c r="G8" t="s" s="826">
+        <v>59</v>
+      </c>
+      <c r="H8" t="n" s="825">
+        <v>2.0</v>
+      </c>
+      <c r="I8" t="n" s="825">
+        <v>3.0</v>
+      </c>
+      <c r="J8" t="s" s="825">
+        <v>15</v>
+      </c>
+      <c r="K8" t="s" s="825">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="824">
+        <v>261</v>
+      </c>
+      <c r="B9" t="s" s="826">
+        <v>59</v>
+      </c>
+      <c r="C9" t="s" s="827">
+        <v>286</v>
+      </c>
+      <c r="D9" t="s" s="826">
+        <v>59</v>
+      </c>
+      <c r="E9" s="828"/>
+      <c r="F9" t="s" s="827">
+        <v>286</v>
+      </c>
+      <c r="G9" t="s" s="826">
+        <v>59</v>
+      </c>
+      <c r="H9" t="n" s="825">
+        <v>3.0</v>
+      </c>
+      <c r="I9" t="n" s="825">
+        <v>2.0</v>
+      </c>
+      <c r="J9" t="s" s="825">
+        <v>104</v>
+      </c>
+      <c r="K9" t="s" s="825">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="824">
+        <v>262</v>
+      </c>
+      <c r="B10" t="s" s="826">
+        <v>90</v>
+      </c>
+      <c r="C10" t="s" s="826">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s" s="826">
+        <v>90</v>
+      </c>
+      <c r="E10" t="s" s="826">
+        <v>90</v>
+      </c>
+      <c r="F10" s="828"/>
+      <c r="G10" t="s" s="826">
+        <v>59</v>
+      </c>
+      <c r="H10" t="n" s="825">
+        <v>5.0</v>
+      </c>
+      <c r="I10" t="n" s="825">
+        <v>0.0</v>
+      </c>
+      <c r="J10" t="s" s="825">
+        <v>158</v>
+      </c>
+      <c r="K10" t="s" s="825">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="824">
+        <v>263</v>
+      </c>
+      <c r="B11" t="s" s="827">
+        <v>269</v>
+      </c>
+      <c r="C11" t="s" s="826">
+        <v>90</v>
+      </c>
+      <c r="D11" t="s" s="827">
+        <v>269</v>
+      </c>
+      <c r="E11" t="s" s="827">
+        <v>269</v>
+      </c>
+      <c r="F11" t="s" s="827">
+        <v>269</v>
+      </c>
+      <c r="G11" s="828"/>
+      <c r="H11" t="n" s="825">
+        <v>1.0</v>
+      </c>
+      <c r="I11" t="n" s="825">
+        <v>4.0</v>
+      </c>
+      <c r="J11" t="s" s="825">
+        <v>153</v>
+      </c>
+      <c r="K11" t="s" s="825">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="822">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="823">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s" s="823">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s" s="823">
+        <v>25</v>
+      </c>
+      <c r="D15" t="s" s="823">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="821">
+        <v>254</v>
+      </c>
+      <c r="B16" t="s" s="821">
+        <v>253</v>
+      </c>
+      <c r="C16" t="s" s="821">
+        <v>61</v>
+      </c>
+      <c r="D16" t="s" s="821">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="821">
+        <v>298</v>
+      </c>
+      <c r="B17" t="s" s="821">
+        <v>253</v>
+      </c>
+      <c r="C17" t="s" s="821">
+        <v>61</v>
+      </c>
+      <c r="D17" t="s" s="821">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="821">
+        <v>194</v>
+      </c>
+      <c r="B18" t="s" s="821">
+        <v>253</v>
+      </c>
+      <c r="C18" t="s" s="821">
+        <v>61</v>
+      </c>
+      <c r="D18" t="s" s="821">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="821">
+        <v>256</v>
+      </c>
+      <c r="B19" t="s" s="821">
+        <v>253</v>
+      </c>
+      <c r="C19" t="s" s="821">
+        <v>92</v>
+      </c>
+      <c r="D19" t="s" s="821">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="821">
+        <v>253</v>
+      </c>
+      <c r="B20" t="s" s="821">
+        <v>257</v>
+      </c>
+      <c r="C20" t="s" s="821">
+        <v>61</v>
+      </c>
+      <c r="D20" t="s" s="821">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="821">
+        <v>254</v>
+      </c>
+      <c r="B21" t="s" s="821">
+        <v>298</v>
+      </c>
+      <c r="C21" t="s" s="821">
+        <v>92</v>
+      </c>
+      <c r="D21" t="s" s="821">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="821">
+        <v>254</v>
+      </c>
+      <c r="B22" t="s" s="821">
+        <v>194</v>
+      </c>
+      <c r="C22" t="s" s="821">
+        <v>92</v>
+      </c>
+      <c r="D22" t="s" s="821">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="821">
+        <v>256</v>
+      </c>
+      <c r="B23" t="s" s="821">
+        <v>254</v>
+      </c>
+      <c r="C23" t="s" s="821">
+        <v>61</v>
+      </c>
+      <c r="D23" t="s" s="821">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="821">
+        <v>257</v>
+      </c>
+      <c r="B24" t="s" s="821">
+        <v>254</v>
+      </c>
+      <c r="C24" t="s" s="821">
+        <v>92</v>
+      </c>
+      <c r="D24" t="s" s="821">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="821">
+        <v>194</v>
+      </c>
+      <c r="B25" t="s" s="821">
+        <v>298</v>
+      </c>
+      <c r="C25" t="s" s="821">
+        <v>61</v>
+      </c>
+      <c r="D25" t="s" s="821">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="821">
+        <v>256</v>
+      </c>
+      <c r="B26" t="s" s="821">
+        <v>298</v>
+      </c>
+      <c r="C26" t="s" s="821">
+        <v>92</v>
+      </c>
+      <c r="D26" t="s" s="821">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="821">
+        <v>298</v>
+      </c>
+      <c r="B27" t="s" s="821">
+        <v>257</v>
+      </c>
+      <c r="C27" t="s" s="821">
+        <v>61</v>
+      </c>
+      <c r="D27" t="s" s="821">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="821">
+        <v>256</v>
+      </c>
+      <c r="B28" t="s" s="821">
+        <v>194</v>
+      </c>
+      <c r="C28" t="s" s="821">
+        <v>92</v>
+      </c>
+      <c r="D28" t="s" s="821">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="821">
+        <v>194</v>
+      </c>
+      <c r="B29" t="s" s="821">
+        <v>257</v>
+      </c>
+      <c r="C29" t="s" s="821">
+        <v>61</v>
+      </c>
+      <c r="D29" t="s" s="821">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="821">
+        <v>256</v>
+      </c>
+      <c r="B30" t="s" s="821">
+        <v>257</v>
+      </c>
+      <c r="C30" t="s" s="821">
+        <v>61</v>
+      </c>
+      <c r="D30" t="s" s="821">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="822">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="821">
+        <v>267</v>
+      </c>
+      <c r="B33" t="s" s="821">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="821">
+        <v>271</v>
+      </c>
+      <c r="B34" t="s" s="821">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="821">
+        <v>209</v>
+      </c>
+      <c r="B35" t="s" s="821">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="821">
+        <v>309</v>
+      </c>
+      <c r="B36" t="s" s="821">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="821">
+        <v>305</v>
+      </c>
+      <c r="B37" t="s" s="821">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="821">
+        <v>285</v>
+      </c>
+      <c r="B38" t="s" s="821">
+        <v>313</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:T132"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
     <col min="1" max="1" width="23.4375" customWidth="true"/>
     <col min="2" max="2" width="16.40625" customWidth="true"/>
     <col min="3" max="3" width="16.40625" customWidth="true"/>
     <col min="4" max="4" width="16.40625" customWidth="true"/>
     <col min="5" max="5" width="16.40625" customWidth="true"/>
-    <col min="6" max="6" width="6.25" customWidth="true"/>
-    <col min="7" max="7" width="6.25" customWidth="true"/>
-    <col min="8" max="8" width="6.25" customWidth="true"/>
-    <col min="9" max="9" width="6.25" customWidth="true"/>
+    <col min="6" max="6" width="16.40625" customWidth="true"/>
+    <col min="7" max="7" width="16.40625" customWidth="true"/>
+    <col min="8" max="8" width="16.40625" customWidth="true"/>
+    <col min="9" max="9" width="16.40625" customWidth="true"/>
+    <col min="10" max="10" width="16.40625" customWidth="true"/>
+    <col min="11" max="11" width="16.40625" customWidth="true"/>
+    <col min="12" max="12" width="16.40625" customWidth="true"/>
+    <col min="13" max="13" width="16.40625" customWidth="true"/>
+    <col min="14" max="14" width="16.40625" customWidth="true"/>
+    <col min="15" max="15" width="16.40625" customWidth="true"/>
+    <col min="16" max="16" width="16.40625" customWidth="true"/>
+    <col min="17" max="17" width="6.25" customWidth="true"/>
+    <col min="18" max="18" width="6.25" customWidth="true"/>
+    <col min="19" max="19" width="6.25" customWidth="true"/>
+    <col min="20" max="20" width="6.25" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="604">
-        <v>223</v>
+      <c r="A1" t="s" s="1783">
+        <v>317</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s" s="605">
-        <v>249</v>
+      <c r="A2" t="s" s="1784">
+        <v>550</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s" s="605">
-        <v>2</v>
+      <c r="A3" t="s" s="1784">
+        <v>252</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s" s="607">
+      <c r="A5" t="s" s="1786">
         <v>3</v>
       </c>
-      <c r="B5" t="s" s="607">
+      <c r="B5" t="s" s="1786">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s" s="1786">
+        <v>319</v>
+      </c>
+      <c r="D5" t="s" s="1786">
+        <v>320</v>
+      </c>
+      <c r="E5" t="s" s="1786">
+        <v>5</v>
+      </c>
+      <c r="F5" t="s" s="1786">
+        <v>6</v>
+      </c>
+      <c r="G5" t="s" s="1786">
         <v>225</v>
       </c>
-      <c r="C5" t="s" s="607">
-        <v>226</v>
-      </c>
-      <c r="D5" t="s" s="607">
+      <c r="H5" t="s" s="1786">
+        <v>7</v>
+      </c>
+      <c r="I5" t="s" s="1786">
+        <v>38</v>
+      </c>
+      <c r="J5" t="s" s="1786">
+        <v>9</v>
+      </c>
+      <c r="K5" t="s" s="1786">
+        <v>321</v>
+      </c>
+      <c r="L5" t="s" s="1786">
+        <v>322</v>
+      </c>
+      <c r="M5" t="s" s="1786">
+        <v>323</v>
+      </c>
+      <c r="N5" t="s" s="1786">
+        <v>52</v>
+      </c>
+      <c r="O5" t="s" s="1786">
+        <v>147</v>
+      </c>
+      <c r="P5" t="s" s="1786">
+        <v>405</v>
+      </c>
+      <c r="Q5" t="s" s="1786">
+        <v>10</v>
+      </c>
+      <c r="R5" t="s" s="1786">
+        <v>11</v>
+      </c>
+      <c r="S5" t="s" s="1786">
+        <v>12</v>
+      </c>
+      <c r="T5" t="s" s="1786">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="1787">
+        <v>42</v>
+      </c>
+      <c r="B6" s="1791"/>
+      <c r="C6" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="D6" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="E6" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="F6" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="G6" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="H6" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="I6" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="J6" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="K6" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="L6" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="M6" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="N6" s="1788"/>
+      <c r="O6" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="P6" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="Q6" t="n" s="1788">
+        <v>11.0</v>
+      </c>
+      <c r="R6" t="n" s="1788">
+        <v>2.0</v>
+      </c>
+      <c r="S6" t="s" s="1788">
+        <v>172</v>
+      </c>
+      <c r="T6" t="s" s="1788">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="1787">
+        <v>324</v>
+      </c>
+      <c r="B7" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="C7" s="1791"/>
+      <c r="D7" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="E7" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="F7" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="G7" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="H7" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="I7" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="J7" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="K7" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="L7" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="M7" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="N7" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="O7" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="P7" s="1788"/>
+      <c r="Q7" t="n" s="1788">
+        <v>2.0</v>
+      </c>
+      <c r="R7" t="n" s="1788">
+        <v>11.0</v>
+      </c>
+      <c r="S7" t="s" s="1788">
+        <v>176</v>
+      </c>
+      <c r="T7" t="s" s="1788">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="1787">
+        <v>325</v>
+      </c>
+      <c r="B8" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="C8" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="D8" s="1791"/>
+      <c r="E8" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="F8" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="G8" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="H8" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="I8" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="J8" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="K8" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="L8" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="M8" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="N8" s="1788"/>
+      <c r="O8" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="P8" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="Q8" t="n" s="1788">
+        <v>6.0</v>
+      </c>
+      <c r="R8" t="n" s="1788">
+        <v>7.0</v>
+      </c>
+      <c r="S8" t="s" s="1788">
+        <v>89</v>
+      </c>
+      <c r="T8" t="s" s="1788">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="1787">
+        <v>326</v>
+      </c>
+      <c r="B9" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="C9" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="D9" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="E9" s="1791"/>
+      <c r="F9" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="G9" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="H9" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="I9" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="J9" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="K9" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="L9" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="M9" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="N9" s="1788"/>
+      <c r="O9" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="P9" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="Q9" t="n" s="1788">
+        <v>8.0</v>
+      </c>
+      <c r="R9" t="n" s="1788">
+        <v>5.0</v>
+      </c>
+      <c r="S9" t="s" s="1788">
+        <v>127</v>
+      </c>
+      <c r="T9" t="s" s="1788">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="1787">
+        <v>327</v>
+      </c>
+      <c r="B10" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="C10" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="D10" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="E10" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="F10" s="1791"/>
+      <c r="G10" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="H10" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="I10" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="J10" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="K10" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="L10" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="M10" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="N10" s="1788"/>
+      <c r="O10" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="P10" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="Q10" t="n" s="1788">
+        <v>3.0</v>
+      </c>
+      <c r="R10" t="n" s="1788">
+        <v>10.0</v>
+      </c>
+      <c r="S10" t="s" s="1788">
+        <v>153</v>
+      </c>
+      <c r="T10" t="s" s="1788">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="1787">
+        <v>328</v>
+      </c>
+      <c r="B11" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="C11" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="D11" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="E11" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="F11" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="G11" s="1791"/>
+      <c r="H11" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="I11" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="J11" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="K11" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="L11" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="M11" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="N11" s="1788"/>
+      <c r="O11" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="P11" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="Q11" t="n" s="1788">
+        <v>6.0</v>
+      </c>
+      <c r="R11" t="n" s="1788">
+        <v>7.0</v>
+      </c>
+      <c r="S11" t="s" s="1788">
+        <v>89</v>
+      </c>
+      <c r="T11" t="s" s="1788">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="1787">
+        <v>329</v>
+      </c>
+      <c r="B12" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="C12" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="D12" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="E12" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="F12" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="G12" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="H12" s="1791"/>
+      <c r="I12" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="J12" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="K12" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="L12" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="M12" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="N12" s="1788"/>
+      <c r="O12" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="P12" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="Q12" t="n" s="1788">
+        <v>5.0</v>
+      </c>
+      <c r="R12" t="n" s="1788">
+        <v>8.0</v>
+      </c>
+      <c r="S12" t="s" s="1788">
+        <v>139</v>
+      </c>
+      <c r="T12" t="s" s="1788">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="1787">
+        <v>330</v>
+      </c>
+      <c r="B13" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="C13" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="D13" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="E13" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="F13" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="G13" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="H13" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="I13" s="1791"/>
+      <c r="J13" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="K13" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="L13" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="M13" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="N13" s="1788"/>
+      <c r="O13" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="P13" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="Q13" t="n" s="1788">
+        <v>12.0</v>
+      </c>
+      <c r="R13" t="n" s="1788">
+        <v>1.0</v>
+      </c>
+      <c r="S13" t="s" s="1788">
+        <v>548</v>
+      </c>
+      <c r="T13" t="s" s="1788">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="1787">
+        <v>331</v>
+      </c>
+      <c r="B14" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="C14" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="D14" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="E14" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="F14" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="G14" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="H14" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="I14" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="J14" s="1791"/>
+      <c r="K14" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="L14" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="M14" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="N14" s="1788"/>
+      <c r="O14" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="P14" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="Q14" t="n" s="1788">
+        <v>11.0</v>
+      </c>
+      <c r="R14" t="n" s="1788">
+        <v>2.0</v>
+      </c>
+      <c r="S14" t="s" s="1788">
+        <v>172</v>
+      </c>
+      <c r="T14" t="s" s="1788">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="1787">
+        <v>332</v>
+      </c>
+      <c r="B15" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="C15" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="D15" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="E15" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="F15" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="G15" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="H15" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="I15" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="J15" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="K15" s="1791"/>
+      <c r="L15" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="M15" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="N15" s="1788"/>
+      <c r="O15" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="P15" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="Q15" t="n" s="1788">
+        <v>7.0</v>
+      </c>
+      <c r="R15" t="n" s="1788">
+        <v>6.0</v>
+      </c>
+      <c r="S15" t="s" s="1788">
+        <v>91</v>
+      </c>
+      <c r="T15" t="s" s="1788">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="1787">
+        <v>333</v>
+      </c>
+      <c r="B16" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="C16" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="D16" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="E16" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="F16" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="G16" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="H16" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="I16" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="J16" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="K16" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="L16" s="1791"/>
+      <c r="M16" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="N16" s="1788"/>
+      <c r="O16" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="P16" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="Q16" t="n" s="1788">
+        <v>2.0</v>
+      </c>
+      <c r="R16" t="n" s="1788">
+        <v>11.0</v>
+      </c>
+      <c r="S16" t="s" s="1788">
+        <v>176</v>
+      </c>
+      <c r="T16" t="s" s="1788">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="1787">
+        <v>334</v>
+      </c>
+      <c r="B17" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="C17" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="D17" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="E17" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="F17" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="G17" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="H17" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="I17" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="J17" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="K17" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="L17" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="M17" s="1791"/>
+      <c r="N17" s="1788"/>
+      <c r="O17" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="P17" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="Q17" t="n" s="1788">
+        <v>3.0</v>
+      </c>
+      <c r="R17" t="n" s="1788">
+        <v>10.0</v>
+      </c>
+      <c r="S17" t="s" s="1788">
+        <v>153</v>
+      </c>
+      <c r="T17" t="s" s="1788">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="1787">
+        <v>406</v>
+      </c>
+      <c r="B18" s="1788"/>
+      <c r="C18" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="D18" s="1788"/>
+      <c r="E18" s="1788"/>
+      <c r="F18" s="1788"/>
+      <c r="G18" s="1788"/>
+      <c r="H18" s="1788"/>
+      <c r="I18" s="1788"/>
+      <c r="J18" s="1788"/>
+      <c r="K18" s="1788"/>
+      <c r="L18" s="1788"/>
+      <c r="M18" s="1788"/>
+      <c r="N18" s="1791"/>
+      <c r="O18" s="1788"/>
+      <c r="P18" s="1788"/>
+      <c r="Q18" t="n" s="1788">
+        <v>1.0</v>
+      </c>
+      <c r="R18" t="n" s="1788">
+        <v>0.0</v>
+      </c>
+      <c r="S18" t="s" s="1788">
+        <v>91</v>
+      </c>
+      <c r="T18" t="s" s="1788">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="1787">
+        <v>336</v>
+      </c>
+      <c r="B19" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="C19" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="D19" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="E19" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="F19" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="G19" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="H19" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="I19" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="J19" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="K19" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="L19" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="M19" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="N19" s="1788"/>
+      <c r="O19" s="1791"/>
+      <c r="P19" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="Q19" t="n" s="1788">
+        <v>6.0</v>
+      </c>
+      <c r="R19" t="n" s="1788">
+        <v>7.0</v>
+      </c>
+      <c r="S19" t="s" s="1788">
+        <v>89</v>
+      </c>
+      <c r="T19" t="s" s="1788">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="1787">
+        <v>407</v>
+      </c>
+      <c r="B20" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="C20" s="1788"/>
+      <c r="D20" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="E20" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="F20" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="G20" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="H20" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="I20" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="J20" t="s" s="1790">
+        <v>233</v>
+      </c>
+      <c r="K20" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="L20" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="M20" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="N20" s="1788"/>
+      <c r="O20" t="s" s="1789">
+        <v>234</v>
+      </c>
+      <c r="P20" s="1791"/>
+      <c r="Q20" t="n" s="1788">
+        <v>8.0</v>
+      </c>
+      <c r="R20" t="n" s="1788">
+        <v>4.0</v>
+      </c>
+      <c r="S20" t="s" s="1788">
+        <v>104</v>
+      </c>
+      <c r="T20" t="s" s="1788">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="1785">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="1786">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s" s="1786">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s" s="1786">
+        <v>25</v>
+      </c>
+      <c r="D24" t="s" s="1786">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="1784">
         <v>37</v>
       </c>
-      <c r="E5" t="s" s="607">
+      <c r="B25" t="s" s="1784">
+        <v>319</v>
+      </c>
+      <c r="C25" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D25" t="s" s="1784">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="1784">
+        <v>320</v>
+      </c>
+      <c r="B26" t="s" s="1784">
+        <v>37</v>
+      </c>
+      <c r="C26" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D26" t="s" s="1784">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="1784">
+        <v>37</v>
+      </c>
+      <c r="B27" t="s" s="1784">
+        <v>5</v>
+      </c>
+      <c r="C27" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D27" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="1784">
+        <v>37</v>
+      </c>
+      <c r="B28" t="s" s="1784">
+        <v>6</v>
+      </c>
+      <c r="C28" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D28" t="s" s="1784">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="1784">
+        <v>37</v>
+      </c>
+      <c r="B29" t="s" s="1784">
+        <v>225</v>
+      </c>
+      <c r="C29" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D29" t="s" s="1784">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="1784">
+        <v>37</v>
+      </c>
+      <c r="B30" t="s" s="1784">
+        <v>7</v>
+      </c>
+      <c r="C30" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D30" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="1784">
+        <v>37</v>
+      </c>
+      <c r="B31" t="s" s="1784">
         <v>38</v>
       </c>
-      <c r="F5" t="s" s="607">
-        <v>10</v>
-      </c>
-      <c r="G5" t="s" s="607">
-        <v>11</v>
-      </c>
-      <c r="H5" t="s" s="607">
-        <v>12</v>
-      </c>
-      <c r="I5" t="s" s="607">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="608">
-        <v>227</v>
-      </c>
-      <c r="B6" s="612"/>
-      <c r="C6" t="s" s="611">
-        <v>233</v>
-      </c>
-      <c r="D6" t="s" s="610">
-        <v>234</v>
-      </c>
-      <c r="E6" t="s" s="611">
-        <v>233</v>
-      </c>
-      <c r="F6" t="n" s="609">
-        <v>1.0</v>
-      </c>
-      <c r="G6" t="n" s="609">
-        <v>2.0</v>
-      </c>
-      <c r="H6" t="s" s="609">
-        <v>89</v>
-      </c>
-      <c r="I6" t="s" s="609">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="608">
-        <v>228</v>
-      </c>
-      <c r="B7" t="s" s="610">
-        <v>234</v>
-      </c>
-      <c r="C7" s="612"/>
-      <c r="D7" t="s" s="610">
-        <v>234</v>
-      </c>
-      <c r="E7" t="s" s="611">
-        <v>233</v>
-      </c>
-      <c r="F7" t="n" s="609">
-        <v>2.0</v>
-      </c>
-      <c r="G7" t="n" s="609">
-        <v>1.0</v>
-      </c>
-      <c r="H7" t="s" s="609">
-        <v>91</v>
-      </c>
-      <c r="I7" t="s" s="609">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="608">
-        <v>229</v>
-      </c>
-      <c r="B8" t="s" s="611">
-        <v>233</v>
-      </c>
-      <c r="C8" t="s" s="611">
-        <v>233</v>
-      </c>
-      <c r="D8" s="612"/>
-      <c r="E8" t="s" s="611">
-        <v>233</v>
-      </c>
-      <c r="F8" t="n" s="609">
-        <v>0.0</v>
-      </c>
-      <c r="G8" t="n" s="609">
-        <v>3.0</v>
-      </c>
-      <c r="H8" t="s" s="609">
-        <v>139</v>
-      </c>
-      <c r="I8" t="s" s="609">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="608">
-        <v>230</v>
-      </c>
-      <c r="B9" t="s" s="610">
-        <v>234</v>
-      </c>
-      <c r="C9" t="s" s="610">
-        <v>234</v>
-      </c>
-      <c r="D9" t="s" s="610">
-        <v>234</v>
-      </c>
-      <c r="E9" s="612"/>
-      <c r="F9" t="n" s="609">
-        <v>3.0</v>
-      </c>
-      <c r="G9" t="n" s="609">
-        <v>0.0</v>
-      </c>
-      <c r="H9" t="s" s="609">
-        <v>127</v>
-      </c>
-      <c r="I9" t="s" s="609">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="606">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="607">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s" s="607">
-        <v>24</v>
-      </c>
-      <c r="C13" t="s" s="607">
-        <v>25</v>
-      </c>
-      <c r="D13" t="s" s="607">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="605">
-        <v>226</v>
-      </c>
-      <c r="B14" t="s" s="605">
+      <c r="C31" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D31" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="1784">
+        <v>9</v>
+      </c>
+      <c r="B32" t="s" s="1784">
+        <v>37</v>
+      </c>
+      <c r="C32" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D32" t="s" s="1784">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="1784">
+        <v>37</v>
+      </c>
+      <c r="B33" t="s" s="1784">
+        <v>321</v>
+      </c>
+      <c r="C33" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D33" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="1784">
+        <v>37</v>
+      </c>
+      <c r="B34" t="s" s="1784">
+        <v>322</v>
+      </c>
+      <c r="C34" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D34" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="1784">
+        <v>37</v>
+      </c>
+      <c r="B35" t="s" s="1784">
+        <v>323</v>
+      </c>
+      <c r="C35" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D35" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="1784">
+        <v>37</v>
+      </c>
+      <c r="B36" t="s" s="1784">
+        <v>147</v>
+      </c>
+      <c r="C36" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D36" t="s" s="1784">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="1784">
+        <v>37</v>
+      </c>
+      <c r="B37" t="s" s="1784">
+        <v>405</v>
+      </c>
+      <c r="C37" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D37" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="1784">
+        <v>319</v>
+      </c>
+      <c r="B38" t="s" s="1784">
+        <v>320</v>
+      </c>
+      <c r="C38" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D38" t="s" s="1784">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="1784">
+        <v>5</v>
+      </c>
+      <c r="B39" t="s" s="1784">
+        <v>319</v>
+      </c>
+      <c r="C39" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D39" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="1784">
+        <v>6</v>
+      </c>
+      <c r="B40" t="s" s="1784">
+        <v>319</v>
+      </c>
+      <c r="C40" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D40" t="s" s="1784">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="1784">
         <v>225</v>
       </c>
-      <c r="C14" t="s" s="605">
+      <c r="B41" t="s" s="1784">
+        <v>319</v>
+      </c>
+      <c r="C41" t="s" s="1784">
         <v>235</v>
       </c>
-      <c r="D14" t="s" s="605">
+      <c r="D41" t="s" s="1784">
         <v>243</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="s" s="605">
+    <row r="42">
+      <c r="A42" t="s" s="1784">
+        <v>7</v>
+      </c>
+      <c r="B42" t="s" s="1784">
+        <v>319</v>
+      </c>
+      <c r="C42" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D42" t="s" s="1784">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="1784">
+        <v>38</v>
+      </c>
+      <c r="B43" t="s" s="1784">
+        <v>319</v>
+      </c>
+      <c r="C43" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D43" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="1784">
+        <v>9</v>
+      </c>
+      <c r="B44" t="s" s="1784">
+        <v>319</v>
+      </c>
+      <c r="C44" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D44" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="1784">
+        <v>321</v>
+      </c>
+      <c r="B45" t="s" s="1784">
+        <v>319</v>
+      </c>
+      <c r="C45" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D45" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="1784">
+        <v>319</v>
+      </c>
+      <c r="B46" t="s" s="1784">
+        <v>322</v>
+      </c>
+      <c r="C46" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D46" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="1784">
+        <v>323</v>
+      </c>
+      <c r="B47" t="s" s="1784">
+        <v>319</v>
+      </c>
+      <c r="C47" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D47" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="1784">
+        <v>52</v>
+      </c>
+      <c r="B48" t="s" s="1784">
+        <v>319</v>
+      </c>
+      <c r="C48" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D48" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="1784">
+        <v>147</v>
+      </c>
+      <c r="B49" t="s" s="1784">
+        <v>319</v>
+      </c>
+      <c r="C49" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D49" t="s" s="1784">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="1784">
+        <v>320</v>
+      </c>
+      <c r="B50" t="s" s="1784">
+        <v>5</v>
+      </c>
+      <c r="C50" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D50" t="s" s="1784">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="1784">
+        <v>6</v>
+      </c>
+      <c r="B51" t="s" s="1784">
+        <v>320</v>
+      </c>
+      <c r="C51" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D51" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="1784">
         <v>225</v>
       </c>
-      <c r="B15" t="s" s="605">
-        <v>37</v>
-      </c>
-      <c r="C15" t="s" s="605">
+      <c r="B52" t="s" s="1784">
+        <v>320</v>
+      </c>
+      <c r="C52" t="s" s="1784">
         <v>235</v>
       </c>
-      <c r="D15" t="s" s="605">
+      <c r="D52" t="s" s="1784">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="1784">
+        <v>7</v>
+      </c>
+      <c r="B53" t="s" s="1784">
+        <v>320</v>
+      </c>
+      <c r="C53" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D53" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="1784">
+        <v>38</v>
+      </c>
+      <c r="B54" t="s" s="1784">
+        <v>320</v>
+      </c>
+      <c r="C54" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D54" t="s" s="1784">
         <v>243</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="s" s="605">
+    <row r="55">
+      <c r="A55" t="s" s="1784">
+        <v>9</v>
+      </c>
+      <c r="B55" t="s" s="1784">
+        <v>320</v>
+      </c>
+      <c r="C55" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D55" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="1784">
+        <v>320</v>
+      </c>
+      <c r="B56" t="s" s="1784">
+        <v>321</v>
+      </c>
+      <c r="C56" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D56" t="s" s="1784">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="1784">
+        <v>320</v>
+      </c>
+      <c r="B57" t="s" s="1784">
+        <v>322</v>
+      </c>
+      <c r="C57" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D57" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="1784">
+        <v>320</v>
+      </c>
+      <c r="B58" t="s" s="1784">
+        <v>323</v>
+      </c>
+      <c r="C58" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D58" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="1784">
+        <v>320</v>
+      </c>
+      <c r="B59" t="s" s="1784">
+        <v>147</v>
+      </c>
+      <c r="C59" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D59" t="s" s="1784">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="1784">
+        <v>405</v>
+      </c>
+      <c r="B60" t="s" s="1784">
+        <v>320</v>
+      </c>
+      <c r="C60" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D60" t="s" s="1784">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="1784">
+        <v>5</v>
+      </c>
+      <c r="B61" t="s" s="1784">
+        <v>6</v>
+      </c>
+      <c r="C61" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D61" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="1784">
+        <v>5</v>
+      </c>
+      <c r="B62" t="s" s="1784">
+        <v>225</v>
+      </c>
+      <c r="C62" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D62" t="s" s="1784">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="1784">
+        <v>5</v>
+      </c>
+      <c r="B63" t="s" s="1784">
+        <v>7</v>
+      </c>
+      <c r="C63" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D63" t="s" s="1784">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="1784">
         <v>38</v>
       </c>
-      <c r="B16" t="s" s="605">
+      <c r="B64" t="s" s="1784">
+        <v>5</v>
+      </c>
+      <c r="C64" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D64" t="s" s="1784">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="1784">
+        <v>5</v>
+      </c>
+      <c r="B65" t="s" s="1784">
+        <v>9</v>
+      </c>
+      <c r="C65" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D65" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="1784">
+        <v>321</v>
+      </c>
+      <c r="B66" t="s" s="1784">
+        <v>5</v>
+      </c>
+      <c r="C66" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D66" t="s" s="1784">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="1784">
+        <v>5</v>
+      </c>
+      <c r="B67" t="s" s="1784">
+        <v>322</v>
+      </c>
+      <c r="C67" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D67" t="s" s="1784">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="1784">
+        <v>5</v>
+      </c>
+      <c r="B68" t="s" s="1784">
+        <v>323</v>
+      </c>
+      <c r="C68" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D68" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="1784">
+        <v>147</v>
+      </c>
+      <c r="B69" t="s" s="1784">
+        <v>5</v>
+      </c>
+      <c r="C69" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D69" t="s" s="1784">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="1784">
+        <v>5</v>
+      </c>
+      <c r="B70" t="s" s="1784">
+        <v>405</v>
+      </c>
+      <c r="C70" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D70" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="1784">
         <v>225</v>
       </c>
-      <c r="C16" t="s" s="605">
+      <c r="B71" t="s" s="1784">
+        <v>6</v>
+      </c>
+      <c r="C71" t="s" s="1784">
         <v>235</v>
       </c>
-      <c r="D16" t="s" s="605">
+      <c r="D71" t="s" s="1784">
         <v>236</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="s" s="605">
-        <v>226</v>
-      </c>
-      <c r="B17" t="s" s="605">
-        <v>37</v>
-      </c>
-      <c r="C17" t="s" s="605">
+    <row r="72">
+      <c r="A72" t="s" s="1784">
+        <v>7</v>
+      </c>
+      <c r="B72" t="s" s="1784">
+        <v>6</v>
+      </c>
+      <c r="C72" t="s" s="1784">
         <v>235</v>
       </c>
-      <c r="D17" t="s" s="605">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="605">
+      <c r="D72" t="s" s="1784">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="1784">
         <v>38</v>
       </c>
-      <c r="B18" t="s" s="605">
-        <v>226</v>
-      </c>
-      <c r="C18" t="s" s="605">
+      <c r="B73" t="s" s="1784">
+        <v>6</v>
+      </c>
+      <c r="C73" t="s" s="1784">
         <v>235</v>
       </c>
-      <c r="D18" t="s" s="605">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="605">
+      <c r="D73" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="1784">
+        <v>9</v>
+      </c>
+      <c r="B74" t="s" s="1784">
+        <v>6</v>
+      </c>
+      <c r="C74" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D74" t="s" s="1784">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="1784">
+        <v>321</v>
+      </c>
+      <c r="B75" t="s" s="1784">
+        <v>6</v>
+      </c>
+      <c r="C75" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D75" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="1784">
+        <v>322</v>
+      </c>
+      <c r="B76" t="s" s="1784">
+        <v>6</v>
+      </c>
+      <c r="C76" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D76" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="1784">
+        <v>323</v>
+      </c>
+      <c r="B77" t="s" s="1784">
+        <v>6</v>
+      </c>
+      <c r="C77" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D77" t="s" s="1784">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="1784">
+        <v>6</v>
+      </c>
+      <c r="B78" t="s" s="1784">
+        <v>147</v>
+      </c>
+      <c r="C78" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D78" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="1784">
+        <v>405</v>
+      </c>
+      <c r="B79" t="s" s="1784">
+        <v>6</v>
+      </c>
+      <c r="C79" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D79" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="1784">
+        <v>225</v>
+      </c>
+      <c r="B80" t="s" s="1784">
+        <v>7</v>
+      </c>
+      <c r="C80" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D80" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="1784">
         <v>38</v>
       </c>
-      <c r="B19" t="s" s="605">
-        <v>37</v>
-      </c>
-      <c r="C19" t="s" s="605">
+      <c r="B81" t="s" s="1784">
+        <v>225</v>
+      </c>
+      <c r="C81" t="s" s="1784">
         <v>235</v>
       </c>
-      <c r="D19" t="s" s="605">
+      <c r="D81" t="s" s="1784">
         <v>246</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="s" s="606">
+    <row r="82">
+      <c r="A82" t="s" s="1784">
+        <v>9</v>
+      </c>
+      <c r="B82" t="s" s="1784">
+        <v>225</v>
+      </c>
+      <c r="C82" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D82" t="s" s="1784">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="1784">
+        <v>321</v>
+      </c>
+      <c r="B83" t="s" s="1784">
+        <v>225</v>
+      </c>
+      <c r="C83" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D83" t="s" s="1784">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="1784">
+        <v>225</v>
+      </c>
+      <c r="B84" t="s" s="1784">
+        <v>322</v>
+      </c>
+      <c r="C84" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D84" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="1784">
+        <v>225</v>
+      </c>
+      <c r="B85" t="s" s="1784">
+        <v>323</v>
+      </c>
+      <c r="C85" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D85" t="s" s="1784">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="1784">
+        <v>147</v>
+      </c>
+      <c r="B86" t="s" s="1784">
+        <v>225</v>
+      </c>
+      <c r="C86" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D86" t="s" s="1784">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="1784">
+        <v>405</v>
+      </c>
+      <c r="B87" t="s" s="1784">
+        <v>225</v>
+      </c>
+      <c r="C87" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D87" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="1784">
+        <v>38</v>
+      </c>
+      <c r="B88" t="s" s="1784">
+        <v>7</v>
+      </c>
+      <c r="C88" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D88" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="1784">
+        <v>9</v>
+      </c>
+      <c r="B89" t="s" s="1784">
+        <v>7</v>
+      </c>
+      <c r="C89" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D89" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="1784">
+        <v>321</v>
+      </c>
+      <c r="B90" t="s" s="1784">
+        <v>7</v>
+      </c>
+      <c r="C90" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D90" t="s" s="1784">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="1784">
+        <v>322</v>
+      </c>
+      <c r="B91" t="s" s="1784">
+        <v>7</v>
+      </c>
+      <c r="C91" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D91" t="s" s="1784">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="1784">
+        <v>7</v>
+      </c>
+      <c r="B92" t="s" s="1784">
+        <v>323</v>
+      </c>
+      <c r="C92" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D92" t="s" s="1784">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="1784">
+        <v>7</v>
+      </c>
+      <c r="B93" t="s" s="1784">
+        <v>147</v>
+      </c>
+      <c r="C93" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D93" t="s" s="1784">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="1784">
+        <v>405</v>
+      </c>
+      <c r="B94" t="s" s="1784">
+        <v>7</v>
+      </c>
+      <c r="C94" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D94" t="s" s="1784">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="1784">
+        <v>38</v>
+      </c>
+      <c r="B95" t="s" s="1784">
+        <v>9</v>
+      </c>
+      <c r="C95" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D95" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="1784">
+        <v>38</v>
+      </c>
+      <c r="B96" t="s" s="1784">
+        <v>321</v>
+      </c>
+      <c r="C96" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D96" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="1784">
+        <v>38</v>
+      </c>
+      <c r="B97" t="s" s="1784">
+        <v>322</v>
+      </c>
+      <c r="C97" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D97" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="1784">
+        <v>38</v>
+      </c>
+      <c r="B98" t="s" s="1784">
+        <v>323</v>
+      </c>
+      <c r="C98" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D98" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="1784">
+        <v>38</v>
+      </c>
+      <c r="B99" t="s" s="1784">
+        <v>147</v>
+      </c>
+      <c r="C99" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D99" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="1784">
+        <v>38</v>
+      </c>
+      <c r="B100" t="s" s="1784">
+        <v>405</v>
+      </c>
+      <c r="C100" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D100" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="1784">
+        <v>9</v>
+      </c>
+      <c r="B101" t="s" s="1784">
+        <v>321</v>
+      </c>
+      <c r="C101" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D101" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="1784">
+        <v>9</v>
+      </c>
+      <c r="B102" t="s" s="1784">
+        <v>322</v>
+      </c>
+      <c r="C102" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D102" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="1784">
+        <v>9</v>
+      </c>
+      <c r="B103" t="s" s="1784">
+        <v>323</v>
+      </c>
+      <c r="C103" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D103" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="1784">
+        <v>9</v>
+      </c>
+      <c r="B104" t="s" s="1784">
+        <v>147</v>
+      </c>
+      <c r="C104" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D104" t="s" s="1784">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="1784">
+        <v>9</v>
+      </c>
+      <c r="B105" t="s" s="1784">
+        <v>405</v>
+      </c>
+      <c r="C105" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D105" t="s" s="1784">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="1784">
+        <v>321</v>
+      </c>
+      <c r="B106" t="s" s="1784">
+        <v>322</v>
+      </c>
+      <c r="C106" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D106" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="1784">
+        <v>321</v>
+      </c>
+      <c r="B107" t="s" s="1784">
+        <v>323</v>
+      </c>
+      <c r="C107" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D107" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="1784">
+        <v>147</v>
+      </c>
+      <c r="B108" t="s" s="1784">
+        <v>321</v>
+      </c>
+      <c r="C108" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D108" t="s" s="1784">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="1784">
+        <v>405</v>
+      </c>
+      <c r="B109" t="s" s="1784">
+        <v>321</v>
+      </c>
+      <c r="C109" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D109" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="1784">
+        <v>323</v>
+      </c>
+      <c r="B110" t="s" s="1784">
+        <v>322</v>
+      </c>
+      <c r="C110" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D110" t="s" s="1784">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="1784">
+        <v>147</v>
+      </c>
+      <c r="B111" t="s" s="1784">
+        <v>322</v>
+      </c>
+      <c r="C111" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D111" t="s" s="1784">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="1784">
+        <v>405</v>
+      </c>
+      <c r="B112" t="s" s="1784">
+        <v>322</v>
+      </c>
+      <c r="C112" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D112" t="s" s="1784">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="1784">
+        <v>147</v>
+      </c>
+      <c r="B113" t="s" s="1784">
+        <v>323</v>
+      </c>
+      <c r="C113" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D113" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="1784">
+        <v>405</v>
+      </c>
+      <c r="B114" t="s" s="1784">
+        <v>323</v>
+      </c>
+      <c r="C114" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D114" t="s" s="1784">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="1784">
+        <v>405</v>
+      </c>
+      <c r="B115" t="s" s="1784">
+        <v>147</v>
+      </c>
+      <c r="C115" t="s" s="1784">
+        <v>235</v>
+      </c>
+      <c r="D115" t="s" s="1784">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="1785">
         <v>28</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="s" s="605">
+    <row r="118">
+      <c r="A118" t="s" s="1784">
         <v>48</v>
       </c>
-      <c r="B22" t="s" s="605">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="605">
-        <v>237</v>
-      </c>
-      <c r="B23" t="s" s="605">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="605">
-        <v>240</v>
-      </c>
-      <c r="B24" t="s" s="605">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="605">
-        <v>100</v>
-      </c>
-      <c r="B25" t="s" s="605">
-        <v>221</v>
+      <c r="B118" t="s" s="1784">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="1784">
+        <v>107</v>
+      </c>
+      <c r="B119" t="s" s="1784">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="1784">
+        <v>123</v>
+      </c>
+      <c r="B120" t="s" s="1784">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="1784">
+        <v>79</v>
+      </c>
+      <c r="B121" t="s" s="1784">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="1784">
+        <v>462</v>
+      </c>
+      <c r="B122" t="s" s="1784">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="1784">
+        <v>436</v>
+      </c>
+      <c r="B123" t="s" s="1784">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="1784">
+        <v>448</v>
+      </c>
+      <c r="B124" t="s" s="1784">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="1784">
+        <v>423</v>
+      </c>
+      <c r="B125" t="s" s="1784">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="1784">
+        <v>422</v>
+      </c>
+      <c r="B126" t="s" s="1784">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="1784">
+        <v>413</v>
+      </c>
+      <c r="B127" t="s" s="1784">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="1784">
+        <v>374</v>
+      </c>
+      <c r="B128" t="s" s="1784">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="1784">
+        <v>430</v>
+      </c>
+      <c r="B129" t="s" s="1784">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="1784">
+        <v>357</v>
+      </c>
+      <c r="B130" t="s" s="1784">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="1784">
+        <v>418</v>
+      </c>
+      <c r="B131" t="s" s="1784">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="1784">
+        <v>523</v>
+      </c>
+      <c r="B132" t="s" s="1784">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/league.xlsx
+++ b/league.xlsx
@@ -12,12 +12,13 @@
     <sheet name="テスト大会_ratetest" r:id="rId7" sheetId="23"/>
     <sheet name="ダブルス大会_2026092101" r:id="rId8" sheetId="24"/>
     <sheet name="シングルス大会_20260921" r:id="rId9" sheetId="25"/>
+    <sheet name="ダブルスリーグ_2026092104" r:id="rId10" sheetId="26"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48867" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51086" uniqueCount="627">
   <si>
     <t>青大会 (blue1)</t>
   </si>
@@ -1670,6 +1671,234 @@
   </si>
   <si>
     <t>シングルス / 5点1セット制(デュース) / 全13フェーズ / 13フェーズ消化</t>
+  </si>
+  <si>
+    <t>ダブルスリーグ (2026092104)</t>
+  </si>
+  <si>
+    <t>ダブルス / 5点2セット制(デュース) / 全5フェーズ / 0フェーズ消化</t>
+  </si>
+  <si>
+    <t>AndroidA &amp; AndroidC</t>
+  </si>
+  <si>
+    <t>LagnaKt &amp; AndroidB</t>
+  </si>
+  <si>
+    <t>hachi_18 &amp; Opanku</t>
+  </si>
+  <si>
+    <t>Rosario20 &amp; Pen4</t>
+  </si>
+  <si>
+    <t>M0nJ &amp; TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>sota2486 &amp; Alpha6000</t>
+  </si>
+  <si>
+    <t>1. AndroidA &amp; AndroidC</t>
+  </si>
+  <si>
+    <t>2. LagnaKt &amp; AndroidB</t>
+  </si>
+  <si>
+    <t>3. hachi_18 &amp; Opanku</t>
+  </si>
+  <si>
+    <t>4. Rosario20 &amp; Pen4</t>
+  </si>
+  <si>
+    <t>5. M0nJ &amp; TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>6. sota2486 &amp; Alpha6000</t>
+  </si>
+  <si>
+    <t>1位  AndroidA &amp; AndroidC</t>
+  </si>
+  <si>
+    <t>1位  LagnaKt &amp; AndroidB</t>
+  </si>
+  <si>
+    <t>1位  hachi_18 &amp; Opanku</t>
+  </si>
+  <si>
+    <t>1位  Rosario20 &amp; Pen4</t>
+  </si>
+  <si>
+    <t>1位  M0nJ &amp; TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>1位  sota2486 &amp; Alpha6000</t>
+  </si>
+  <si>
+    <t>sota2486 &amp; M0nJ</t>
+  </si>
+  <si>
+    <t>Alpha6000 &amp; hachi_18</t>
+  </si>
+  <si>
+    <t>Pen4 &amp; Rosario20</t>
+  </si>
+  <si>
+    <t>Opanku &amp; TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>1. LagnaKt &amp; AndroidB</t>
+  </si>
+  <si>
+    <t>2. AndroidA &amp; AndroidC</t>
+  </si>
+  <si>
+    <t>3. sota2486 &amp; M0nJ</t>
+  </si>
+  <si>
+    <t>4. Alpha6000 &amp; hachi_18</t>
+  </si>
+  <si>
+    <t>5. Pen4 &amp; Rosario20</t>
+  </si>
+  <si>
+    <t>6. Opanku &amp; TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>1位  sota2486 &amp; M0nJ</t>
+  </si>
+  <si>
+    <t>1位  Alpha6000 &amp; hachi_18</t>
+  </si>
+  <si>
+    <t>1位  Pen4 &amp; Rosario20</t>
+  </si>
+  <si>
+    <t>1位  Opanku &amp; TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>2位  LagnaKt &amp; AndroidB</t>
+  </si>
+  <si>
+    <t>2位  AndroidA &amp; AndroidC</t>
+  </si>
+  <si>
+    <t>2位  Pen4 &amp; Rosario20</t>
+  </si>
+  <si>
+    <t>2位  Opanku &amp; TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>6位  Alpha6000 &amp; hachi_18</t>
+  </si>
+  <si>
+    <t>7-5 5-1</t>
+  </si>
+  <si>
+    <t>3位  AndroidA &amp; AndroidC</t>
+  </si>
+  <si>
+    <t>3位  Pen4 &amp; Rosario20</t>
+  </si>
+  <si>
+    <t>5位  Alpha6000 &amp; hachi_18</t>
+  </si>
+  <si>
+    <t>5位  Opanku &amp; TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>7-5 5-3</t>
+  </si>
+  <si>
+    <t>4位  AndroidA &amp; AndroidC</t>
+  </si>
+  <si>
+    <t>4位  Alpha6000 &amp; hachi_18</t>
+  </si>
+  <si>
+    <t>4位  Opanku &amp; TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>ダブルス / 5点2セット制(デュース) / 全5フェーズ / 1フェーズ消化</t>
+  </si>
+  <si>
+    <t>5-0 5-3</t>
+  </si>
+  <si>
+    <t>5位  AndroidA &amp; AndroidC</t>
+  </si>
+  <si>
+    <t>2-5 5-1 5-2</t>
+  </si>
+  <si>
+    <t>7-5 0-5 5-0</t>
+  </si>
+  <si>
+    <t>3位  LagnaKt &amp; AndroidB</t>
+  </si>
+  <si>
+    <t>3位  Alpha6000 &amp; hachi_18</t>
+  </si>
+  <si>
+    <t>ダブルス / 5点2セット制(デュース) / 全5フェーズ / 2フェーズ消化</t>
+  </si>
+  <si>
+    <t>× 0-0</t>
+  </si>
+  <si>
+    <t>○ 0-0</t>
+  </si>
+  <si>
+    <t>0-0</t>
+  </si>
+  <si>
+    <t>2位  sota2486 &amp; M0nJ</t>
+  </si>
+  <si>
+    <t>0-5 5-3 5-1</t>
+  </si>
+  <si>
+    <t>6位  AndroidA &amp; AndroidC</t>
+  </si>
+  <si>
+    <t>ダブルス / 5点2セット制(デュース) / 全5フェーズ / 3フェーズ消化</t>
+  </si>
+  <si>
+    <t>1勝3敗  得失セット-4</t>
+  </si>
+  <si>
+    <t>5-1 1-5 5-3</t>
+  </si>
+  <si>
+    <t>3勝1敗  得失セット+4</t>
+  </si>
+  <si>
+    <t>3位  sota2486 &amp; M0nJ</t>
+  </si>
+  <si>
+    <t>2勝2敗  得失セット+2</t>
+  </si>
+  <si>
+    <t>4-6 5-2 7-5</t>
+  </si>
+  <si>
+    <t>ダブルス / 5点2セット制(デュース) / 全5フェーズ / 4フェーズ消化</t>
+  </si>
+  <si>
+    <t>5-1 5-1</t>
+  </si>
+  <si>
+    <t>4勝1敗  得失セット+6</t>
+  </si>
+  <si>
+    <t>6位  Opanku &amp; TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>1勝4敗  得失セット-6</t>
+  </si>
+  <si>
+    <t>5勝0敗  得失セット+6</t>
+  </si>
+  <si>
+    <t>ダブルス / 5点2セット制(デュース) / 全5フェーズ / 5フェーズ消化</t>
   </si>
 </sst>
 </file>
@@ -1677,13 +1906,358 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="598">
+  <fonts count="667">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -4726,7 +5300,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1792">
+  <cellXfs count="1999">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -8506,6 +9080,443 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="596" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="598" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="598" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="598" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="600" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="599" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="601" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="601" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="601" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="603" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="602" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="604" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="604" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="604" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="606" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="605" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="607" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="607" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="607" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="609" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="608" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="610" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="610" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="610" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="612" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="611" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="613" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="613" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="613" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="615" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="614" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="616" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="616" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="616" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="618" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="617" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="619" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="619" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="619" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="621" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="620" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="622" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="622" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="622" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="624" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="623" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="625" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="625" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="625" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="627" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="626" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="628" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="628" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="628" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="630" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="629" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="631" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="631" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="631" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="633" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="632" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="634" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="634" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="634" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="636" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="635" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="637" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="637" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="637" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="639" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="638" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="640" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="640" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="640" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="642" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="641" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="643" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="643" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="643" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="645" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="644" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="646" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="646" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="646" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="648" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="647" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="649" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="649" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="649" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="651" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="650" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="652" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="652" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="652" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="654" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="653" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="655" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="655" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="655" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="657" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="656" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="658" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="658" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="658" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="660" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="659" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="661" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="661" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="661" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="663" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="662" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="664" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="664" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="664" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="666" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="665" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
@@ -10845,26 +11856,26 @@
   <dimension ref="A1:T132"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="23.4375" customWidth="true"/>
-    <col min="2" max="2" width="16.40625" customWidth="true"/>
-    <col min="3" max="3" width="16.40625" customWidth="true"/>
-    <col min="4" max="4" width="16.40625" customWidth="true"/>
-    <col min="5" max="5" width="16.40625" customWidth="true"/>
-    <col min="6" max="6" width="16.40625" customWidth="true"/>
-    <col min="7" max="7" width="16.40625" customWidth="true"/>
-    <col min="8" max="8" width="16.40625" customWidth="true"/>
-    <col min="9" max="9" width="16.40625" customWidth="true"/>
-    <col min="10" max="10" width="16.40625" customWidth="true"/>
-    <col min="11" max="11" width="16.40625" customWidth="true"/>
-    <col min="12" max="12" width="16.40625" customWidth="true"/>
-    <col min="13" max="13" width="16.40625" customWidth="true"/>
-    <col min="14" max="14" width="16.40625" customWidth="true"/>
-    <col min="15" max="15" width="16.40625" customWidth="true"/>
-    <col min="16" max="16" width="16.40625" customWidth="true"/>
-    <col min="17" max="17" width="6.25" customWidth="true"/>
-    <col min="18" max="18" width="6.25" customWidth="true"/>
-    <col min="19" max="19" width="6.25" customWidth="true"/>
-    <col min="20" max="20" width="6.25" customWidth="true"/>
+    <col min="1" max="1" customWidth="true" width="23.4375"/>
+    <col min="2" max="2" customWidth="true" width="16.40625"/>
+    <col min="3" max="3" customWidth="true" width="16.40625"/>
+    <col min="4" max="4" customWidth="true" width="16.40625"/>
+    <col min="5" max="5" customWidth="true" width="16.40625"/>
+    <col min="6" max="6" customWidth="true" width="16.40625"/>
+    <col min="7" max="7" customWidth="true" width="16.40625"/>
+    <col min="8" max="8" customWidth="true" width="16.40625"/>
+    <col min="9" max="9" customWidth="true" width="16.40625"/>
+    <col min="10" max="10" customWidth="true" width="16.40625"/>
+    <col min="11" max="11" customWidth="true" width="16.40625"/>
+    <col min="12" max="12" customWidth="true" width="16.40625"/>
+    <col min="13" max="13" customWidth="true" width="16.40625"/>
+    <col min="14" max="14" customWidth="true" width="16.40625"/>
+    <col min="15" max="15" customWidth="true" width="16.40625"/>
+    <col min="16" max="16" customWidth="true" width="16.40625"/>
+    <col min="17" max="17" customWidth="true" width="6.25"/>
+    <col min="18" max="18" customWidth="true" width="6.25"/>
+    <col min="19" max="19" customWidth="true" width="6.25"/>
+    <col min="20" max="20" customWidth="true" width="6.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13209,4 +14220,554 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:K38"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="23.4375" customWidth="true"/>
+    <col min="2" max="2" width="16.40625" customWidth="true"/>
+    <col min="3" max="3" width="16.40625" customWidth="true"/>
+    <col min="4" max="4" width="16.40625" customWidth="true"/>
+    <col min="5" max="5" width="16.40625" customWidth="true"/>
+    <col min="6" max="6" width="16.40625" customWidth="true"/>
+    <col min="7" max="7" width="16.40625" customWidth="true"/>
+    <col min="8" max="8" width="6.25" customWidth="true"/>
+    <col min="9" max="9" width="6.25" customWidth="true"/>
+    <col min="10" max="10" width="6.25" customWidth="true"/>
+    <col min="11" max="11" width="6.25" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1990">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="1991">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="1991">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="1993">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s" s="1993">
+        <v>554</v>
+      </c>
+      <c r="C5" t="s" s="1993">
+        <v>553</v>
+      </c>
+      <c r="D5" t="s" s="1993">
+        <v>571</v>
+      </c>
+      <c r="E5" t="s" s="1993">
+        <v>572</v>
+      </c>
+      <c r="F5" t="s" s="1993">
+        <v>573</v>
+      </c>
+      <c r="G5" t="s" s="1993">
+        <v>574</v>
+      </c>
+      <c r="H5" t="s" s="1993">
+        <v>10</v>
+      </c>
+      <c r="I5" t="s" s="1993">
+        <v>11</v>
+      </c>
+      <c r="J5" t="s" s="1993">
+        <v>12</v>
+      </c>
+      <c r="K5" t="s" s="1993">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="1994">
+        <v>575</v>
+      </c>
+      <c r="B6" s="1998"/>
+      <c r="C6" t="s" s="1996">
+        <v>59</v>
+      </c>
+      <c r="D6" t="s" s="1996">
+        <v>90</v>
+      </c>
+      <c r="E6" t="s" s="1996">
+        <v>59</v>
+      </c>
+      <c r="F6" t="s" s="1997">
+        <v>286</v>
+      </c>
+      <c r="G6" t="s" s="1996">
+        <v>59</v>
+      </c>
+      <c r="H6" t="n" s="1995">
+        <v>4.0</v>
+      </c>
+      <c r="I6" t="n" s="1995">
+        <v>1.0</v>
+      </c>
+      <c r="J6" t="s" s="1995">
+        <v>124</v>
+      </c>
+      <c r="K6" t="s" s="1995">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="1994">
+        <v>576</v>
+      </c>
+      <c r="B7" t="s" s="1997">
+        <v>269</v>
+      </c>
+      <c r="C7" s="1998"/>
+      <c r="D7" t="s" s="1997">
+        <v>286</v>
+      </c>
+      <c r="E7" t="s" s="1996">
+        <v>59</v>
+      </c>
+      <c r="F7" t="s" s="1997">
+        <v>269</v>
+      </c>
+      <c r="G7" t="s" s="1997">
+        <v>286</v>
+      </c>
+      <c r="H7" t="n" s="1995">
+        <v>1.0</v>
+      </c>
+      <c r="I7" t="n" s="1995">
+        <v>4.0</v>
+      </c>
+      <c r="J7" t="s" s="1995">
+        <v>103</v>
+      </c>
+      <c r="K7" t="s" s="1995">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="1994">
+        <v>577</v>
+      </c>
+      <c r="B8" t="s" s="1997">
+        <v>286</v>
+      </c>
+      <c r="C8" t="s" s="1996">
+        <v>90</v>
+      </c>
+      <c r="D8" s="1998"/>
+      <c r="E8" t="s" s="1996">
+        <v>59</v>
+      </c>
+      <c r="F8" t="s" s="1997">
+        <v>607</v>
+      </c>
+      <c r="G8" t="s" s="1996">
+        <v>59</v>
+      </c>
+      <c r="H8" t="n" s="1995">
+        <v>3.0</v>
+      </c>
+      <c r="I8" t="n" s="1995">
+        <v>2.0</v>
+      </c>
+      <c r="J8" t="s" s="1995">
+        <v>104</v>
+      </c>
+      <c r="K8" t="s" s="1995">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="1994">
+        <v>578</v>
+      </c>
+      <c r="B9" t="s" s="1997">
+        <v>269</v>
+      </c>
+      <c r="C9" t="s" s="1997">
+        <v>269</v>
+      </c>
+      <c r="D9" t="s" s="1997">
+        <v>269</v>
+      </c>
+      <c r="E9" s="1998"/>
+      <c r="F9" t="s" s="1997">
+        <v>269</v>
+      </c>
+      <c r="G9" t="s" s="1996">
+        <v>59</v>
+      </c>
+      <c r="H9" t="n" s="1995">
+        <v>1.0</v>
+      </c>
+      <c r="I9" t="n" s="1995">
+        <v>4.0</v>
+      </c>
+      <c r="J9" t="s" s="1995">
+        <v>465</v>
+      </c>
+      <c r="K9" t="s" s="1995">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="1994">
+        <v>579</v>
+      </c>
+      <c r="B10" t="s" s="1996">
+        <v>90</v>
+      </c>
+      <c r="C10" t="s" s="1996">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s" s="1996">
+        <v>608</v>
+      </c>
+      <c r="E10" t="s" s="1996">
+        <v>59</v>
+      </c>
+      <c r="F10" s="1998"/>
+      <c r="G10" t="s" s="1996">
+        <v>90</v>
+      </c>
+      <c r="H10" t="n" s="1995">
+        <v>5.0</v>
+      </c>
+      <c r="I10" t="n" s="1995">
+        <v>0.0</v>
+      </c>
+      <c r="J10" t="s" s="1995">
+        <v>124</v>
+      </c>
+      <c r="K10" t="s" s="1995">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="1994">
+        <v>580</v>
+      </c>
+      <c r="B11" t="s" s="1997">
+        <v>269</v>
+      </c>
+      <c r="C11" t="s" s="1996">
+        <v>90</v>
+      </c>
+      <c r="D11" t="s" s="1997">
+        <v>269</v>
+      </c>
+      <c r="E11" t="s" s="1997">
+        <v>269</v>
+      </c>
+      <c r="F11" t="s" s="1997">
+        <v>286</v>
+      </c>
+      <c r="G11" s="1998"/>
+      <c r="H11" t="n" s="1995">
+        <v>1.0</v>
+      </c>
+      <c r="I11" t="n" s="1995">
+        <v>4.0</v>
+      </c>
+      <c r="J11" t="s" s="1995">
+        <v>465</v>
+      </c>
+      <c r="K11" t="s" s="1995">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="1992">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="1993">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s" s="1993">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s" s="1993">
+        <v>25</v>
+      </c>
+      <c r="D15" t="s" s="1993">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="1991">
+        <v>554</v>
+      </c>
+      <c r="B16" t="s" s="1991">
+        <v>553</v>
+      </c>
+      <c r="C16" t="s" s="1991">
+        <v>61</v>
+      </c>
+      <c r="D16" t="s" s="1991">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="1991">
+        <v>554</v>
+      </c>
+      <c r="B17" t="s" s="1991">
+        <v>571</v>
+      </c>
+      <c r="C17" t="s" s="1991">
+        <v>92</v>
+      </c>
+      <c r="D17" t="s" s="1991">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="1991">
+        <v>554</v>
+      </c>
+      <c r="B18" t="s" s="1991">
+        <v>572</v>
+      </c>
+      <c r="C18" t="s" s="1991">
+        <v>61</v>
+      </c>
+      <c r="D18" t="s" s="1991">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="1991">
+        <v>573</v>
+      </c>
+      <c r="B19" t="s" s="1991">
+        <v>554</v>
+      </c>
+      <c r="C19" t="s" s="1991">
+        <v>92</v>
+      </c>
+      <c r="D19" t="s" s="1991">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="1991">
+        <v>554</v>
+      </c>
+      <c r="B20" t="s" s="1991">
+        <v>574</v>
+      </c>
+      <c r="C20" t="s" s="1991">
+        <v>61</v>
+      </c>
+      <c r="D20" t="s" s="1991">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="1991">
+        <v>571</v>
+      </c>
+      <c r="B21" t="s" s="1991">
+        <v>553</v>
+      </c>
+      <c r="C21" t="s" s="1991">
+        <v>92</v>
+      </c>
+      <c r="D21" t="s" s="1991">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="1991">
+        <v>553</v>
+      </c>
+      <c r="B22" t="s" s="1991">
+        <v>572</v>
+      </c>
+      <c r="C22" t="s" s="1991">
+        <v>61</v>
+      </c>
+      <c r="D22" t="s" s="1991">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="1991">
+        <v>573</v>
+      </c>
+      <c r="B23" t="s" s="1991">
+        <v>553</v>
+      </c>
+      <c r="C23" t="s" s="1991">
+        <v>61</v>
+      </c>
+      <c r="D23" t="s" s="1991">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="1991">
+        <v>574</v>
+      </c>
+      <c r="B24" t="s" s="1991">
+        <v>553</v>
+      </c>
+      <c r="C24" t="s" s="1991">
+        <v>92</v>
+      </c>
+      <c r="D24" t="s" s="1991">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="1991">
+        <v>571</v>
+      </c>
+      <c r="B25" t="s" s="1991">
+        <v>572</v>
+      </c>
+      <c r="C25" t="s" s="1991">
+        <v>61</v>
+      </c>
+      <c r="D25" t="s" s="1991">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="1991">
+        <v>573</v>
+      </c>
+      <c r="B26" t="s" s="1991">
+        <v>571</v>
+      </c>
+      <c r="C26" t="s" s="1991">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="1991">
+        <v>571</v>
+      </c>
+      <c r="B27" t="s" s="1991">
+        <v>574</v>
+      </c>
+      <c r="C27" t="s" s="1991">
+        <v>61</v>
+      </c>
+      <c r="D27" t="s" s="1991">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="1991">
+        <v>573</v>
+      </c>
+      <c r="B28" t="s" s="1991">
+        <v>572</v>
+      </c>
+      <c r="C28" t="s" s="1991">
+        <v>61</v>
+      </c>
+      <c r="D28" t="s" s="1991">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="1991">
+        <v>572</v>
+      </c>
+      <c r="B29" t="s" s="1991">
+        <v>574</v>
+      </c>
+      <c r="C29" t="s" s="1991">
+        <v>61</v>
+      </c>
+      <c r="D29" t="s" s="1991">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="1991">
+        <v>573</v>
+      </c>
+      <c r="B30" t="s" s="1991">
+        <v>574</v>
+      </c>
+      <c r="C30" t="s" s="1991">
+        <v>92</v>
+      </c>
+      <c r="D30" t="s" s="1991">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="1992">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="1991">
+        <v>583</v>
+      </c>
+      <c r="B33" t="s" s="1991">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="1991">
+        <v>585</v>
+      </c>
+      <c r="B34" t="s" s="1991">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="1991">
+        <v>617</v>
+      </c>
+      <c r="B35" t="s" s="1991">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="1991">
+        <v>596</v>
+      </c>
+      <c r="B36" t="s" s="1991">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="1991">
+        <v>593</v>
+      </c>
+      <c r="B37" t="s" s="1991">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="1991">
+        <v>594</v>
+      </c>
+      <c r="B38" t="s" s="1991">
+        <v>624</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>